--- a/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>YRD</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44469</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43921</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43373</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43190</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43008</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42916</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42825</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>182800</v>
+        <v>182200</v>
       </c>
       <c r="E8" s="3">
-        <v>136200</v>
+        <v>184100</v>
       </c>
       <c r="F8" s="3">
-        <v>150200</v>
+        <v>137100</v>
       </c>
       <c r="G8" s="3">
-        <v>116100</v>
+        <v>151300</v>
       </c>
       <c r="H8" s="3">
-        <v>207900</v>
+        <v>116900</v>
       </c>
       <c r="I8" s="3">
-        <v>141000</v>
+        <v>209400</v>
       </c>
       <c r="J8" s="3">
+        <v>141900</v>
+      </c>
+      <c r="K8" s="3">
         <v>170100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>159900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>156400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>166700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>142400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>105100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>149500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>388500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>316600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>345800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>302600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>431100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>317700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>418100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>540200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>270800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>224700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>175600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>148600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>155800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>127500</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>47800</v>
+        <v>34100</v>
       </c>
       <c r="E9" s="3">
-        <v>27600</v>
+        <v>48200</v>
       </c>
       <c r="F9" s="3">
-        <v>29200</v>
+        <v>27800</v>
       </c>
       <c r="G9" s="3">
-        <v>30900</v>
+        <v>29400</v>
       </c>
       <c r="H9" s="3">
-        <v>47200</v>
+        <v>31100</v>
       </c>
       <c r="I9" s="3">
-        <v>29900</v>
+        <v>47500</v>
       </c>
       <c r="J9" s="3">
+        <v>30100</v>
+      </c>
+      <c r="K9" s="3">
         <v>25800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>26000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>24800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>85700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>33400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>24000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>25400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>33000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>38100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>43000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>38000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>21800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>17700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>135000</v>
+        <v>148100</v>
       </c>
       <c r="E10" s="3">
-        <v>108600</v>
+        <v>135900</v>
       </c>
       <c r="F10" s="3">
-        <v>121000</v>
+        <v>109300</v>
       </c>
       <c r="G10" s="3">
-        <v>85200</v>
+        <v>121900</v>
       </c>
       <c r="H10" s="3">
-        <v>160800</v>
+        <v>85800</v>
       </c>
       <c r="I10" s="3">
-        <v>111000</v>
+        <v>161900</v>
       </c>
       <c r="J10" s="3">
+        <v>111800</v>
+      </c>
+      <c r="K10" s="3">
         <v>144300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>134000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>131600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>81000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>109000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>82100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>134500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>361700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>292600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>320400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>276300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>398100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>279600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>375100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>502200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>249000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>207000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>161800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>140000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>147500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>120600</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,13 +1083,14 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>5400</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1156,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1253,20 +1273,20 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1274,11 +1294,11 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>94200</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1295,8 +1315,8 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1328,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1414,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>90200</v>
+        <v>85800</v>
       </c>
       <c r="E17" s="3">
-        <v>61200</v>
+        <v>90800</v>
       </c>
       <c r="F17" s="3">
-        <v>63000</v>
+        <v>61600</v>
       </c>
       <c r="G17" s="3">
-        <v>69700</v>
+        <v>63400</v>
       </c>
       <c r="H17" s="3">
-        <v>138300</v>
+        <v>70200</v>
       </c>
       <c r="I17" s="3">
-        <v>95600</v>
+        <v>139300</v>
       </c>
       <c r="J17" s="3">
+        <v>96200</v>
+      </c>
+      <c r="K17" s="3">
         <v>112800</v>
-      </c>
-      <c r="K17" s="3">
-        <v>119500</v>
       </c>
       <c r="L17" s="3">
         <v>119500</v>
       </c>
       <c r="M17" s="3">
+        <v>119500</v>
+      </c>
+      <c r="N17" s="3">
         <v>248700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>126600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>141300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>147800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>286800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>281700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>319500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>267200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>295500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>341600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>406400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>455900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>191700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>168600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>120200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>91400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>98100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>92700</v>
+        <v>96400</v>
       </c>
       <c r="E18" s="3">
-        <v>75000</v>
+        <v>93300</v>
       </c>
       <c r="F18" s="3">
-        <v>87300</v>
+        <v>75500</v>
       </c>
       <c r="G18" s="3">
-        <v>46300</v>
+        <v>87900</v>
       </c>
       <c r="H18" s="3">
-        <v>69600</v>
+        <v>46700</v>
       </c>
       <c r="I18" s="3">
-        <v>45400</v>
+        <v>70100</v>
       </c>
       <c r="J18" s="3">
+        <v>45700</v>
+      </c>
+      <c r="K18" s="3">
         <v>57300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>40400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>36800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-82000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-36200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>101700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>34900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>26300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>35400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>135600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-23900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>84200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>79100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>56100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>55400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>57100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>57700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,180 +1680,187 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
-        <v>600</v>
-      </c>
       <c r="H20" s="3">
+        <v>700</v>
+      </c>
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-27000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>7400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>32700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>12300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>21400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>92100</v>
+        <v>99600</v>
       </c>
       <c r="E21" s="3">
-        <v>76200</v>
+        <v>92700</v>
       </c>
       <c r="F21" s="3">
-        <v>88200</v>
+        <v>76700</v>
       </c>
       <c r="G21" s="3">
-        <v>46000</v>
+        <v>88800</v>
       </c>
       <c r="H21" s="3">
-        <v>72600</v>
+        <v>46400</v>
       </c>
       <c r="I21" s="3">
-        <v>44800</v>
+        <v>73100</v>
       </c>
       <c r="J21" s="3">
+        <v>45100</v>
+      </c>
+      <c r="K21" s="3">
         <v>54300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>35900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>34200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-89000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-39300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>76700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>38300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>33500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>73100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>164200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-14800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>33000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>94400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>81200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>58000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>59400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>61500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>59800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1905,180 +1945,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>92100</v>
+        <v>99600</v>
       </c>
       <c r="E23" s="3">
-        <v>75900</v>
+        <v>92700</v>
       </c>
       <c r="F23" s="3">
-        <v>89000</v>
+        <v>76400</v>
       </c>
       <c r="G23" s="3">
-        <v>47000</v>
+        <v>89600</v>
       </c>
       <c r="H23" s="3">
-        <v>70500</v>
+        <v>47300</v>
       </c>
       <c r="I23" s="3">
-        <v>44900</v>
+        <v>71000</v>
       </c>
       <c r="J23" s="3">
+        <v>45200</v>
+      </c>
+      <c r="K23" s="3">
         <v>54800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>36300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>32100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-88000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-38900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>74700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>38200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>33700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>68100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>147900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-14600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>33100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>88900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>81100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>57700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>59300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>60900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>59700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F24" s="3">
+        <v>17100</v>
+      </c>
+      <c r="G24" s="3">
+        <v>22100</v>
+      </c>
+      <c r="H24" s="3">
+        <v>9700</v>
+      </c>
+      <c r="I24" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K24" s="3">
+        <v>10500</v>
+      </c>
+      <c r="L24" s="3">
+        <v>7900</v>
+      </c>
+      <c r="M24" s="3">
+        <v>6300</v>
+      </c>
+      <c r="N24" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="O24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P24" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>600</v>
+      </c>
+      <c r="R24" s="3">
+        <v>12500</v>
+      </c>
+      <c r="S24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="T24" s="3">
+        <v>9700</v>
+      </c>
+      <c r="U24" s="3">
+        <v>11700</v>
+      </c>
+      <c r="V24" s="3">
+        <v>4700</v>
+      </c>
+      <c r="W24" s="3">
+        <v>5100</v>
+      </c>
+      <c r="X24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>12000</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>14500</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>12700</v>
+      </c>
+      <c r="AB24" s="3">
         <v>19300</v>
       </c>
-      <c r="E24" s="3">
-        <v>16900</v>
-      </c>
-      <c r="F24" s="3">
-        <v>22000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>9700</v>
-      </c>
-      <c r="H24" s="3">
-        <v>9800</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J24" s="3">
-        <v>10500</v>
-      </c>
-      <c r="K24" s="3">
-        <v>7900</v>
-      </c>
-      <c r="L24" s="3">
-        <v>6300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="N24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="P24" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>12500</v>
-      </c>
-      <c r="R24" s="3">
-        <v>3100</v>
-      </c>
-      <c r="S24" s="3">
-        <v>9700</v>
-      </c>
-      <c r="T24" s="3">
-        <v>11700</v>
-      </c>
-      <c r="U24" s="3">
-        <v>4700</v>
-      </c>
-      <c r="V24" s="3">
-        <v>5100</v>
-      </c>
-      <c r="W24" s="3">
-        <v>6000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>12000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>14500</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>12700</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>19300</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>72800</v>
+        <v>77100</v>
       </c>
       <c r="E26" s="3">
-        <v>59000</v>
+        <v>73300</v>
       </c>
       <c r="F26" s="3">
-        <v>67000</v>
+        <v>59400</v>
       </c>
       <c r="G26" s="3">
-        <v>37300</v>
+        <v>67500</v>
       </c>
       <c r="H26" s="3">
-        <v>60700</v>
+        <v>37600</v>
       </c>
       <c r="I26" s="3">
-        <v>45700</v>
+        <v>61100</v>
       </c>
       <c r="J26" s="3">
+        <v>46000</v>
+      </c>
+      <c r="K26" s="3">
         <v>44300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>28400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>25800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-80400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-32300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>62200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>35100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>24100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>56400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>143200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-19700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>27100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>76900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>66600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>45000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>39900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>51000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>55200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>72800</v>
+        <v>77100</v>
       </c>
       <c r="E27" s="3">
-        <v>59000</v>
+        <v>73300</v>
       </c>
       <c r="F27" s="3">
-        <v>67000</v>
+        <v>59400</v>
       </c>
       <c r="G27" s="3">
-        <v>37300</v>
+        <v>67500</v>
       </c>
       <c r="H27" s="3">
-        <v>60700</v>
+        <v>37600</v>
       </c>
       <c r="I27" s="3">
-        <v>45700</v>
+        <v>61100</v>
       </c>
       <c r="J27" s="3">
+        <v>46000</v>
+      </c>
+      <c r="K27" s="3">
         <v>44300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>28400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>25800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-80400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-32300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>62200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>35100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>56400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>143200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-19700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>27100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>76900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>66600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>45000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>39900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>51000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>55200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
-        <v>-600</v>
-      </c>
       <c r="H32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>27000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-7400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-32700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-12300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-21400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>72800</v>
+        <v>77100</v>
       </c>
       <c r="E33" s="3">
-        <v>59000</v>
+        <v>73300</v>
       </c>
       <c r="F33" s="3">
-        <v>67000</v>
+        <v>59400</v>
       </c>
       <c r="G33" s="3">
-        <v>37300</v>
+        <v>67500</v>
       </c>
       <c r="H33" s="3">
-        <v>60700</v>
+        <v>37600</v>
       </c>
       <c r="I33" s="3">
-        <v>45700</v>
+        <v>61100</v>
       </c>
       <c r="J33" s="3">
+        <v>46000</v>
+      </c>
+      <c r="K33" s="3">
         <v>44300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>28400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>25800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-80400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-32300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>62200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>56400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>143200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-19700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>27100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>76900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>66600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>45000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>39900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>51000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>55200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>72800</v>
+        <v>77100</v>
       </c>
       <c r="E35" s="3">
-        <v>59000</v>
+        <v>73300</v>
       </c>
       <c r="F35" s="3">
-        <v>67000</v>
+        <v>59400</v>
       </c>
       <c r="G35" s="3">
-        <v>37300</v>
+        <v>67500</v>
       </c>
       <c r="H35" s="3">
-        <v>60700</v>
+        <v>37600</v>
       </c>
       <c r="I35" s="3">
-        <v>45700</v>
+        <v>61100</v>
       </c>
       <c r="J35" s="3">
+        <v>46000</v>
+      </c>
+      <c r="K35" s="3">
         <v>44300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>28400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>25800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-80400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-32300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>62200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>56400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>143200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-19700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>27100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>76900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>66600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>45000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>39900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>51000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>55200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44469</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43921</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43373</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43190</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43008</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42916</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42825</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,94 +3264,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>802100</v>
+        <v>756000</v>
       </c>
       <c r="E41" s="3">
-        <v>701100</v>
+        <v>807500</v>
       </c>
       <c r="F41" s="3">
-        <v>589900</v>
+        <v>705800</v>
       </c>
       <c r="G41" s="3">
-        <v>498900</v>
+        <v>593900</v>
       </c>
       <c r="H41" s="3">
-        <v>601300</v>
+        <v>502300</v>
       </c>
       <c r="I41" s="3">
-        <v>395500</v>
+        <v>605400</v>
       </c>
       <c r="J41" s="3">
+        <v>398200</v>
+      </c>
+      <c r="K41" s="3">
         <v>321500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>311700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>335800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>354700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>394800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>408600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>466600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>492400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>405400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>422200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>384900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>378600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>117200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>79400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>239200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>275600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>208300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>132300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>125700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>140800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>160900</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3350,94 +3440,100 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>219400</v>
+        <v>190900</v>
       </c>
       <c r="E43" s="3">
-        <v>221200</v>
+        <v>220900</v>
       </c>
       <c r="F43" s="3">
-        <v>205400</v>
+        <v>222700</v>
       </c>
       <c r="G43" s="3">
-        <v>193200</v>
+        <v>206800</v>
       </c>
       <c r="H43" s="3">
-        <v>170300</v>
+        <v>194500</v>
       </c>
       <c r="I43" s="3">
-        <v>163500</v>
+        <v>171500</v>
       </c>
       <c r="J43" s="3">
+        <v>164600</v>
+      </c>
+      <c r="K43" s="3">
         <v>141900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>183800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>150700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>144600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>234500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>221000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>236200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>152800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>268800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>283700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>52100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>203600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>18700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>20100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>20600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>29800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3300</v>
       </c>
-      <c r="AB43" s="3" t="s">
+      <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4400</v>
       </c>
-      <c r="AD43" s="3" t="s">
+      <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3522,94 +3618,100 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>41000</v>
+        <v>37900</v>
       </c>
       <c r="E45" s="3">
-        <v>35700</v>
+        <v>41300</v>
       </c>
       <c r="F45" s="3">
-        <v>44400</v>
+        <v>36000</v>
       </c>
       <c r="G45" s="3">
-        <v>49900</v>
+        <v>44700</v>
       </c>
       <c r="H45" s="3">
-        <v>36800</v>
+        <v>50200</v>
       </c>
       <c r="I45" s="3">
-        <v>48600</v>
+        <v>37100</v>
       </c>
       <c r="J45" s="3">
+        <v>48900</v>
+      </c>
+      <c r="K45" s="3">
         <v>49400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>40000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>137400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>157900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>126800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>205300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>197200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>178300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>186600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>370700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>171500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>171900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>170900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>158600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>168700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>91700</v>
       </c>
-      <c r="AB45" s="3" t="s">
+      <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>67900</v>
       </c>
-      <c r="AD45" s="3" t="s">
+      <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3694,180 +3796,189 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>202700</v>
+        <v>269700</v>
       </c>
       <c r="E47" s="3">
-        <v>194800</v>
+        <v>204100</v>
       </c>
       <c r="F47" s="3">
-        <v>299700</v>
+        <v>196100</v>
       </c>
       <c r="G47" s="3">
-        <v>322900</v>
+        <v>301800</v>
       </c>
       <c r="H47" s="3">
+        <v>325100</v>
+      </c>
+      <c r="I47" s="3">
+        <v>257600</v>
+      </c>
+      <c r="J47" s="3">
+        <v>425000</v>
+      </c>
+      <c r="K47" s="3">
+        <v>486500</v>
+      </c>
+      <c r="L47" s="3">
+        <v>446600</v>
+      </c>
+      <c r="M47" s="3">
+        <v>398400</v>
+      </c>
+      <c r="N47" s="3">
+        <v>341000</v>
+      </c>
+      <c r="O47" s="3">
+        <v>305200</v>
+      </c>
+      <c r="P47" s="3">
+        <v>302800</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>391500</v>
+      </c>
+      <c r="R47" s="3">
+        <v>510400</v>
+      </c>
+      <c r="S47" s="3">
+        <v>578100</v>
+      </c>
+      <c r="T47" s="3">
+        <v>655400</v>
+      </c>
+      <c r="U47" s="3">
+        <v>909100</v>
+      </c>
+      <c r="V47" s="3">
+        <v>968300</v>
+      </c>
+      <c r="W47" s="3">
+        <v>688300</v>
+      </c>
+      <c r="X47" s="3">
+        <v>707400</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>617000</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>261900</v>
+      </c>
+      <c r="AA47" s="3">
         <v>255800</v>
       </c>
-      <c r="I47" s="3">
-        <v>422100</v>
-      </c>
-      <c r="J47" s="3">
-        <v>486500</v>
-      </c>
-      <c r="K47" s="3">
-        <v>446600</v>
-      </c>
-      <c r="L47" s="3">
-        <v>398400</v>
-      </c>
-      <c r="M47" s="3">
-        <v>341000</v>
-      </c>
-      <c r="N47" s="3">
-        <v>305200</v>
-      </c>
-      <c r="O47" s="3">
-        <v>302800</v>
-      </c>
-      <c r="P47" s="3">
-        <v>391500</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>510400</v>
-      </c>
-      <c r="R47" s="3">
-        <v>578100</v>
-      </c>
-      <c r="S47" s="3">
-        <v>655400</v>
-      </c>
-      <c r="T47" s="3">
-        <v>909100</v>
-      </c>
-      <c r="U47" s="3">
-        <v>968300</v>
-      </c>
-      <c r="V47" s="3">
-        <v>688300</v>
-      </c>
-      <c r="W47" s="3">
-        <v>707400</v>
-      </c>
-      <c r="X47" s="3">
-        <v>617000</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>261900</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>255800</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>314900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>297700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>236800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13700</v>
+        <v>14000</v>
       </c>
       <c r="E48" s="3">
-        <v>14500</v>
+        <v>13800</v>
       </c>
       <c r="F48" s="3">
-        <v>15300</v>
+        <v>14600</v>
       </c>
       <c r="G48" s="3">
-        <v>16800</v>
+        <v>15500</v>
       </c>
       <c r="H48" s="3">
-        <v>19500</v>
+        <v>16900</v>
       </c>
       <c r="I48" s="3">
-        <v>25300</v>
+        <v>19600</v>
       </c>
       <c r="J48" s="3">
+        <v>25500</v>
+      </c>
+      <c r="K48" s="3">
         <v>25700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>30900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>36300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>45200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>56900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>70100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>81600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>92000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>98000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>96100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>38600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8900</v>
       </c>
-      <c r="AB48" s="3" t="s">
+      <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5200</v>
       </c>
-      <c r="AD48" s="3" t="s">
+      <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,94 +4241,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>14900</v>
+        <v>31400</v>
       </c>
       <c r="E52" s="3">
-        <v>20100</v>
+        <v>15000</v>
       </c>
       <c r="F52" s="3">
-        <v>23900</v>
+        <v>20300</v>
       </c>
       <c r="G52" s="3">
-        <v>20900</v>
+        <v>24000</v>
       </c>
       <c r="H52" s="3">
-        <v>20500</v>
+        <v>21000</v>
       </c>
       <c r="I52" s="3">
-        <v>12200</v>
+        <v>20600</v>
       </c>
       <c r="J52" s="3">
+        <v>12300</v>
+      </c>
+      <c r="K52" s="3">
         <v>13500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>36500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>19500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>36100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>41400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>38800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>88800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>50000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>152900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>290800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>386900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>361500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>337900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>205100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>240600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>141700</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1293900</v>
+        <v>1300000</v>
       </c>
       <c r="E54" s="3">
-        <v>1187500</v>
+        <v>1302700</v>
       </c>
       <c r="F54" s="3">
-        <v>1178700</v>
+        <v>1195600</v>
       </c>
       <c r="G54" s="3">
-        <v>1102800</v>
+        <v>1186700</v>
       </c>
       <c r="H54" s="3">
-        <v>1104600</v>
+        <v>1110300</v>
       </c>
       <c r="I54" s="3">
-        <v>1068700</v>
+        <v>1112100</v>
       </c>
       <c r="J54" s="3">
+        <v>1075900</v>
+      </c>
+      <c r="K54" s="3">
         <v>1043400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1023500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>987300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>962600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1165300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1187000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1325500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1485000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1599600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1701200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1689500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2069800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1059600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1142900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1349900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1115800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1036300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>888900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>782000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>695600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>586200</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,94 +4576,98 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="L57" s="3">
         <v>9200</v>
       </c>
-      <c r="E57" s="3">
-        <v>2700</v>
-      </c>
-      <c r="F57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>5100</v>
-      </c>
-      <c r="K57" s="3">
-        <v>9200</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>44600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4800</v>
-      </c>
-      <c r="W57" s="3">
-        <v>5100</v>
       </c>
       <c r="X57" s="3">
         <v>5100</v>
       </c>
       <c r="Y57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Z57" s="3">
         <v>5000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2200</v>
       </c>
-      <c r="AB57" s="3" t="s">
+      <c r="AC57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2000</v>
       </c>
-      <c r="AD57" s="3" t="s">
+      <c r="AE57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4618,94 +4752,100 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>247500</v>
+        <v>213900</v>
       </c>
       <c r="E59" s="3">
-        <v>223700</v>
+        <v>249200</v>
       </c>
       <c r="F59" s="3">
-        <v>217900</v>
+        <v>225200</v>
       </c>
       <c r="G59" s="3">
-        <v>215300</v>
+        <v>219400</v>
       </c>
       <c r="H59" s="3">
-        <v>242100</v>
+        <v>216800</v>
       </c>
       <c r="I59" s="3">
-        <v>240200</v>
+        <v>243700</v>
       </c>
       <c r="J59" s="3">
+        <v>241900</v>
+      </c>
+      <c r="K59" s="3">
         <v>251900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>264100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>291000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>332300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>337200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>330000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>338400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>420000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>456400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>433100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>431000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1611500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>224200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>361500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>189000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>220600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>277900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>152400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>55300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>205500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>51700</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4790,44 +4930,47 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>54100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>54100</v>
+        <v>54500</v>
       </c>
       <c r="F61" s="3">
-        <v>106000</v>
+        <v>54500</v>
       </c>
       <c r="G61" s="3">
-        <v>106000</v>
+        <v>106800</v>
       </c>
       <c r="H61" s="3">
-        <v>120000</v>
+        <v>106800</v>
       </c>
       <c r="I61" s="3">
-        <v>142000</v>
+        <v>120900</v>
       </c>
       <c r="J61" s="3">
+        <v>143000</v>
+      </c>
+      <c r="K61" s="3">
         <v>143400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>137700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>113600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>71900</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -4876,85 +5019,88 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13800</v>
+        <v>16500</v>
       </c>
       <c r="E62" s="3">
-        <v>11700</v>
+        <v>13900</v>
       </c>
       <c r="F62" s="3">
+        <v>11800</v>
+      </c>
+      <c r="G62" s="3">
+        <v>11100</v>
+      </c>
+      <c r="H62" s="3">
         <v>11000</v>
       </c>
-      <c r="G62" s="3">
-        <v>10900</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11100</v>
       </c>
-      <c r="I62" s="3">
-        <v>15500</v>
-      </c>
       <c r="J62" s="3">
+        <v>15600</v>
+      </c>
+      <c r="K62" s="3">
         <v>20400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>22600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>31600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>33700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>41200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>51400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>63800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>70700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>81500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>92100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>90000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>8900</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>329200</v>
+        <v>253300</v>
       </c>
       <c r="E66" s="3">
-        <v>297400</v>
+        <v>331500</v>
       </c>
       <c r="F66" s="3">
-        <v>345900</v>
+        <v>299400</v>
       </c>
       <c r="G66" s="3">
-        <v>336700</v>
+        <v>348300</v>
       </c>
       <c r="H66" s="3">
-        <v>378400</v>
+        <v>339000</v>
       </c>
       <c r="I66" s="3">
-        <v>402900</v>
+        <v>381000</v>
       </c>
       <c r="J66" s="3">
+        <v>405700</v>
+      </c>
+      <c r="K66" s="3">
         <v>423200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>431800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>424600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>420000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>561000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>594000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>670600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>793700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1149400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1282900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1302400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2122600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>366300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>501700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>726100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>675100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>665900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>480400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>420000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>384400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>333000</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>257000</v>
+        <v>335700</v>
       </c>
       <c r="E72" s="3">
-        <v>184300</v>
+        <v>258700</v>
       </c>
       <c r="F72" s="3">
-        <v>125500</v>
+        <v>185600</v>
       </c>
       <c r="G72" s="3">
-        <v>58600</v>
+        <v>126400</v>
       </c>
       <c r="H72" s="3">
-        <v>26200</v>
+        <v>59000</v>
       </c>
       <c r="I72" s="3">
-        <v>-34200</v>
+        <v>26400</v>
       </c>
       <c r="J72" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="K72" s="3">
         <v>-79800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-124900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-153100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-180600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-97000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-108100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-79200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-82100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-144200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-181100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-200200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>310400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>506800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>475500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>459100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>272300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>207200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>264700</v>
       </c>
-      <c r="AB72" s="3" t="s">
+      <c r="AC72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>171200</v>
       </c>
-      <c r="AD72" s="3" t="s">
+      <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>964700</v>
+        <v>1046700</v>
       </c>
       <c r="E76" s="3">
-        <v>890100</v>
+        <v>971300</v>
       </c>
       <c r="F76" s="3">
-        <v>832700</v>
+        <v>896200</v>
       </c>
       <c r="G76" s="3">
-        <v>766000</v>
+        <v>838400</v>
       </c>
       <c r="H76" s="3">
-        <v>726100</v>
+        <v>771200</v>
       </c>
       <c r="I76" s="3">
-        <v>665700</v>
+        <v>731100</v>
       </c>
       <c r="J76" s="3">
+        <v>670300</v>
+      </c>
+      <c r="K76" s="3">
         <v>620200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>591700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>562700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>542500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>604300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>593000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>654900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>691400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>450200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>418300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>387000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-52800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>693400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>641200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>623800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>440800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>370400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>408500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>361900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>311200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>253200</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44469</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43921</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43373</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43190</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43008</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42916</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42825</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>72800</v>
+        <v>77100</v>
       </c>
       <c r="E81" s="3">
-        <v>59000</v>
+        <v>73300</v>
       </c>
       <c r="F81" s="3">
-        <v>67000</v>
+        <v>59400</v>
       </c>
       <c r="G81" s="3">
-        <v>37300</v>
+        <v>67500</v>
       </c>
       <c r="H81" s="3">
-        <v>60700</v>
+        <v>37600</v>
       </c>
       <c r="I81" s="3">
-        <v>45700</v>
+        <v>61100</v>
       </c>
       <c r="J81" s="3">
+        <v>46000</v>
+      </c>
+      <c r="K81" s="3">
         <v>44300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>28400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>25800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-80400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-32300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>62200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>56400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>143200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-19700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>27100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>76900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>66600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>45000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>39900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>51000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>55200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6493,8 +6692,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>99100</v>
+        <v>89700</v>
       </c>
       <c r="E89" s="3">
-        <v>53900</v>
+        <v>99800</v>
       </c>
       <c r="F89" s="3">
-        <v>65200</v>
+        <v>54300</v>
       </c>
       <c r="G89" s="3">
-        <v>47300</v>
+        <v>65600</v>
       </c>
       <c r="H89" s="3">
-        <v>142900</v>
+        <v>47700</v>
       </c>
       <c r="I89" s="3">
-        <v>26100</v>
+        <v>143800</v>
       </c>
       <c r="J89" s="3">
+        <v>26300</v>
+      </c>
+      <c r="K89" s="3">
         <v>44700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-20200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-31500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>81400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>13600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>181100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-51800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-100600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>149000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-20100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-191800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-48500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>189300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>51400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>78700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>82100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>121600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,8 +7261,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7127,8 +7348,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-54800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2800</v>
       </c>
-      <c r="E94" s="3">
-        <v>106900</v>
-      </c>
       <c r="F94" s="3">
-        <v>39100</v>
+        <v>107600</v>
       </c>
       <c r="G94" s="3">
-        <v>-115300</v>
+        <v>39400</v>
       </c>
       <c r="H94" s="3">
-        <v>83500</v>
+        <v>-116100</v>
       </c>
       <c r="I94" s="3">
-        <v>52700</v>
+        <v>84000</v>
       </c>
       <c r="J94" s="3">
+        <v>53100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-32300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-40700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-140900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-76600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>314600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-199000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>91300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-34500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>127200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>322400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>65700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-37700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-28700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>50800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-62200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-117500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-98800</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,115 +8004,121 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-800</v>
+        <v>-69900</v>
       </c>
       <c r="E100" s="3">
-        <v>-54200</v>
+        <v>-900</v>
       </c>
       <c r="F100" s="3">
-        <v>-7500</v>
+        <v>-54600</v>
       </c>
       <c r="G100" s="3">
-        <v>-38100</v>
+        <v>-7600</v>
       </c>
       <c r="H100" s="3">
-        <v>-21900</v>
+        <v>-38400</v>
       </c>
       <c r="I100" s="3">
-        <v>-6300</v>
+        <v>-22000</v>
       </c>
       <c r="J100" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="K100" s="3">
         <v>6900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>20500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>39700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>129200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>11400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-242800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-11400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>75400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-10500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-15300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-11800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>33900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-86300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-14100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>8800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
@@ -7880,143 +8129,149 @@
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>95600</v>
+        <v>-34600</v>
       </c>
       <c r="E102" s="3">
-        <v>106500</v>
+        <v>96200</v>
       </c>
       <c r="F102" s="3">
-        <v>96600</v>
+        <v>107300</v>
       </c>
       <c r="G102" s="3">
-        <v>-105800</v>
+        <v>97200</v>
       </c>
       <c r="H102" s="3">
-        <v>204600</v>
+        <v>-106500</v>
       </c>
       <c r="I102" s="3">
-        <v>72500</v>
+        <v>206000</v>
       </c>
       <c r="J102" s="3">
+        <v>73000</v>
+      </c>
+      <c r="K102" s="3">
         <v>19300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-39500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-21100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-43300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-29500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>85100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>31900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-63600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>149000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-231900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-111400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>75600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>81000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>49500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>12800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>15400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-7000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>YRD</t>
   </si>
@@ -656,403 +656,415 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>182200</v>
+        <v>176100</v>
       </c>
       <c r="E8" s="3">
-        <v>184100</v>
+        <v>181100</v>
       </c>
       <c r="F8" s="3">
-        <v>137100</v>
+        <v>183000</v>
       </c>
       <c r="G8" s="3">
-        <v>151300</v>
+        <v>136300</v>
       </c>
       <c r="H8" s="3">
-        <v>116900</v>
+        <v>150300</v>
       </c>
       <c r="I8" s="3">
-        <v>209400</v>
+        <v>116200</v>
       </c>
       <c r="J8" s="3">
+        <v>208100</v>
+      </c>
+      <c r="K8" s="3">
         <v>141900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>170100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>159900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>156400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>166700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>142400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>105100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>149500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>388500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>316600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>345800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>302600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>431100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>317700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>418100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>540200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>270800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>224700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>175600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>148600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>155800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>127500</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>34100</v>
+        <v>25500</v>
       </c>
       <c r="E9" s="3">
-        <v>48200</v>
+        <v>33900</v>
       </c>
       <c r="F9" s="3">
-        <v>27800</v>
+        <v>47900</v>
       </c>
       <c r="G9" s="3">
-        <v>29400</v>
+        <v>27600</v>
       </c>
       <c r="H9" s="3">
-        <v>31100</v>
+        <v>29200</v>
       </c>
       <c r="I9" s="3">
-        <v>47500</v>
+        <v>30900</v>
       </c>
       <c r="J9" s="3">
+        <v>47200</v>
+      </c>
+      <c r="K9" s="3">
         <v>30100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>25800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>24800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>85700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>33400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>23000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>24000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>25400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>33000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>38100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>43000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>38000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>21800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>17700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>148100</v>
+        <v>150500</v>
       </c>
       <c r="E10" s="3">
-        <v>135900</v>
+        <v>147200</v>
       </c>
       <c r="F10" s="3">
-        <v>109300</v>
+        <v>135100</v>
       </c>
       <c r="G10" s="3">
-        <v>121900</v>
+        <v>108700</v>
       </c>
       <c r="H10" s="3">
-        <v>85800</v>
+        <v>121100</v>
       </c>
       <c r="I10" s="3">
-        <v>161900</v>
+        <v>85300</v>
       </c>
       <c r="J10" s="3">
+        <v>160900</v>
+      </c>
+      <c r="K10" s="3">
         <v>111800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>144300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>134000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>131600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>81000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>109000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>82100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>134500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>361700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>292600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>320400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>276300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>398100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>279600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>375100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>502200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>249000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>207000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>161800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>140000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>147500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>120600</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,16 +1096,17 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E12" s="3">
         <v>5400</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1173,8 +1186,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1278,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1276,20 +1295,20 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1297,11 +1316,11 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>94200</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1318,8 +1337,8 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1351,8 +1370,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1462,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1495,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>85800</v>
+        <v>81100</v>
       </c>
       <c r="E17" s="3">
-        <v>90800</v>
+        <v>85300</v>
       </c>
       <c r="F17" s="3">
-        <v>61600</v>
+        <v>90200</v>
       </c>
       <c r="G17" s="3">
-        <v>63400</v>
+        <v>61300</v>
       </c>
       <c r="H17" s="3">
-        <v>70200</v>
+        <v>63000</v>
       </c>
       <c r="I17" s="3">
-        <v>139300</v>
+        <v>69800</v>
       </c>
       <c r="J17" s="3">
+        <v>138400</v>
+      </c>
+      <c r="K17" s="3">
         <v>96200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>112800</v>
-      </c>
-      <c r="L17" s="3">
-        <v>119500</v>
       </c>
       <c r="M17" s="3">
         <v>119500</v>
       </c>
       <c r="N17" s="3">
+        <v>119500</v>
+      </c>
+      <c r="O17" s="3">
         <v>248700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>126600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>141300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>147800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>286800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>281700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>319500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>267200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>295500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>341600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>406400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>455900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>191700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>168600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>120200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>91400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>98100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>96400</v>
+        <v>94900</v>
       </c>
       <c r="E18" s="3">
-        <v>93300</v>
+        <v>95800</v>
       </c>
       <c r="F18" s="3">
-        <v>75500</v>
+        <v>92700</v>
       </c>
       <c r="G18" s="3">
-        <v>87900</v>
+        <v>75000</v>
       </c>
       <c r="H18" s="3">
-        <v>46700</v>
+        <v>87300</v>
       </c>
       <c r="I18" s="3">
-        <v>70100</v>
+        <v>46400</v>
       </c>
       <c r="J18" s="3">
+        <v>69700</v>
+      </c>
+      <c r="K18" s="3">
         <v>45700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>57300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>40400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>36800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-82000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-36200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>101700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>34900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>26300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>35400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>135600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-23900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>84200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>79100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>56100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>55400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>57100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>57700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,186 +1713,193 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E20" s="3">
         <v>3200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3">
-        <v>700</v>
-      </c>
       <c r="I20" s="3">
+        <v>600</v>
+      </c>
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-27000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>7400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>32700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>12300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>9300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>21400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>99600</v>
+        <v>98400</v>
       </c>
       <c r="E21" s="3">
-        <v>92700</v>
+        <v>99000</v>
       </c>
       <c r="F21" s="3">
+        <v>92200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>76200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>88200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>46100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>72700</v>
+      </c>
+      <c r="K21" s="3">
+        <v>45100</v>
+      </c>
+      <c r="L21" s="3">
+        <v>54300</v>
+      </c>
+      <c r="M21" s="3">
+        <v>35900</v>
+      </c>
+      <c r="N21" s="3">
+        <v>34200</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-89000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>13300</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="R21" s="3">
+        <v>7300</v>
+      </c>
+      <c r="S21" s="3">
         <v>76700</v>
       </c>
-      <c r="G21" s="3">
-        <v>88800</v>
-      </c>
-      <c r="H21" s="3">
-        <v>46400</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="T21" s="3">
+        <v>38300</v>
+      </c>
+      <c r="U21" s="3">
+        <v>33500</v>
+      </c>
+      <c r="V21" s="3">
         <v>73100</v>
       </c>
-      <c r="J21" s="3">
-        <v>45100</v>
-      </c>
-      <c r="K21" s="3">
-        <v>54300</v>
-      </c>
-      <c r="L21" s="3">
-        <v>35900</v>
-      </c>
-      <c r="M21" s="3">
-        <v>34200</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-89000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>13300</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-39300</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>7300</v>
-      </c>
-      <c r="R21" s="3">
-        <v>76700</v>
-      </c>
-      <c r="S21" s="3">
-        <v>38300</v>
-      </c>
-      <c r="T21" s="3">
-        <v>33500</v>
-      </c>
-      <c r="U21" s="3">
-        <v>73100</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>164200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-14800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>33000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>94400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>81200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>58000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>59400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>61500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>59800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1948,186 +1987,195 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>99600</v>
+        <v>98400</v>
       </c>
       <c r="E23" s="3">
-        <v>92700</v>
+        <v>99000</v>
       </c>
       <c r="F23" s="3">
-        <v>76400</v>
+        <v>92200</v>
       </c>
       <c r="G23" s="3">
-        <v>89600</v>
+        <v>76000</v>
       </c>
       <c r="H23" s="3">
-        <v>47300</v>
+        <v>89000</v>
       </c>
       <c r="I23" s="3">
-        <v>71000</v>
+        <v>47000</v>
       </c>
       <c r="J23" s="3">
+        <v>70500</v>
+      </c>
+      <c r="K23" s="3">
         <v>45200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>54800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>36300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>32100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-88000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-38900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>74700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>38200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>33700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>68100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>147900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-14600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>33100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>88900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>81100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>57700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>59300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>60900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>59700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>22500</v>
+        <v>19500</v>
       </c>
       <c r="E24" s="3">
-        <v>19400</v>
+        <v>22400</v>
       </c>
       <c r="F24" s="3">
-        <v>17100</v>
+        <v>19300</v>
       </c>
       <c r="G24" s="3">
-        <v>22100</v>
+        <v>16900</v>
       </c>
       <c r="H24" s="3">
+        <v>22000</v>
+      </c>
+      <c r="I24" s="3">
         <v>9700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L24" s="3">
+        <v>10500</v>
+      </c>
+      <c r="M24" s="3">
+        <v>7900</v>
+      </c>
+      <c r="N24" s="3">
+        <v>6300</v>
+      </c>
+      <c r="O24" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="P24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="R24" s="3">
+        <v>600</v>
+      </c>
+      <c r="S24" s="3">
+        <v>12500</v>
+      </c>
+      <c r="T24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="U24" s="3">
+        <v>9700</v>
+      </c>
+      <c r="V24" s="3">
+        <v>11700</v>
+      </c>
+      <c r="W24" s="3">
+        <v>4700</v>
+      </c>
+      <c r="X24" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>14500</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>12700</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>19300</v>
+      </c>
+      <c r="AD24" s="3">
         <v>9900</v>
       </c>
-      <c r="J24" s="3">
-        <v>-700</v>
-      </c>
-      <c r="K24" s="3">
-        <v>10500</v>
-      </c>
-      <c r="L24" s="3">
-        <v>7900</v>
-      </c>
-      <c r="M24" s="3">
-        <v>6300</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="O24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>600</v>
-      </c>
-      <c r="R24" s="3">
-        <v>12500</v>
-      </c>
-      <c r="S24" s="3">
-        <v>3100</v>
-      </c>
-      <c r="T24" s="3">
-        <v>9700</v>
-      </c>
-      <c r="U24" s="3">
-        <v>11700</v>
-      </c>
-      <c r="V24" s="3">
-        <v>4700</v>
-      </c>
-      <c r="W24" s="3">
-        <v>5100</v>
-      </c>
-      <c r="X24" s="3">
-        <v>6000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>12000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>14500</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>12700</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>19300</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>9900</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2263,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>77100</v>
+        <v>78900</v>
       </c>
       <c r="E26" s="3">
-        <v>73300</v>
+        <v>76600</v>
       </c>
       <c r="F26" s="3">
-        <v>59400</v>
+        <v>72900</v>
       </c>
       <c r="G26" s="3">
-        <v>67500</v>
+        <v>59000</v>
       </c>
       <c r="H26" s="3">
-        <v>37600</v>
+        <v>67000</v>
       </c>
       <c r="I26" s="3">
-        <v>61100</v>
+        <v>37300</v>
       </c>
       <c r="J26" s="3">
+        <v>60700</v>
+      </c>
+      <c r="K26" s="3">
         <v>46000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>44300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>28400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>25800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-80400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>11100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>62200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>35100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>24100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>56400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>143200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-19700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>27100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>76900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>66600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>45000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>39900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>51000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>55200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>77100</v>
+        <v>78900</v>
       </c>
       <c r="E27" s="3">
-        <v>73300</v>
+        <v>76600</v>
       </c>
       <c r="F27" s="3">
-        <v>59400</v>
+        <v>72900</v>
       </c>
       <c r="G27" s="3">
-        <v>67500</v>
+        <v>59000</v>
       </c>
       <c r="H27" s="3">
-        <v>37600</v>
+        <v>67000</v>
       </c>
       <c r="I27" s="3">
-        <v>61100</v>
+        <v>37300</v>
       </c>
       <c r="J27" s="3">
+        <v>60700</v>
+      </c>
+      <c r="K27" s="3">
         <v>46000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>44300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>28400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>25800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-80400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>62200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>35100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>24100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>56400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>143200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-19700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>27100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>76900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>66600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>45000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>39900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>51000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>55200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2539,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2631,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2723,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2815,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3">
-        <v>-700</v>
-      </c>
       <c r="I32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>27000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-7400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-32700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-12300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-9300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-21400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>77100</v>
+        <v>78900</v>
       </c>
       <c r="E33" s="3">
-        <v>73300</v>
+        <v>76600</v>
       </c>
       <c r="F33" s="3">
-        <v>59400</v>
+        <v>72900</v>
       </c>
       <c r="G33" s="3">
-        <v>67500</v>
+        <v>59000</v>
       </c>
       <c r="H33" s="3">
-        <v>37600</v>
+        <v>67000</v>
       </c>
       <c r="I33" s="3">
-        <v>61100</v>
+        <v>37300</v>
       </c>
       <c r="J33" s="3">
+        <v>60700</v>
+      </c>
+      <c r="K33" s="3">
         <v>46000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>44300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>28400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>25800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-80400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>62200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>35100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>24100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>56400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>143200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-19700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>27100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>76900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>66600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>45000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>39900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>51000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>55200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3091,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>77100</v>
+        <v>78900</v>
       </c>
       <c r="E35" s="3">
-        <v>73300</v>
+        <v>76600</v>
       </c>
       <c r="F35" s="3">
-        <v>59400</v>
+        <v>72900</v>
       </c>
       <c r="G35" s="3">
-        <v>67500</v>
+        <v>59000</v>
       </c>
       <c r="H35" s="3">
-        <v>37600</v>
+        <v>67000</v>
       </c>
       <c r="I35" s="3">
-        <v>61100</v>
+        <v>37300</v>
       </c>
       <c r="J35" s="3">
+        <v>60700</v>
+      </c>
+      <c r="K35" s="3">
         <v>46000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>44300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>28400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>25800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-80400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>62200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>35100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>24100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>56400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>143200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-19700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>27100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>76900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>66600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>45000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>39900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>51000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>55200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3316,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3350,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>756000</v>
+        <v>800100</v>
       </c>
       <c r="E41" s="3">
-        <v>807500</v>
+        <v>751300</v>
       </c>
       <c r="F41" s="3">
-        <v>705800</v>
+        <v>802500</v>
       </c>
       <c r="G41" s="3">
-        <v>593900</v>
+        <v>701500</v>
       </c>
       <c r="H41" s="3">
-        <v>502300</v>
+        <v>590200</v>
       </c>
       <c r="I41" s="3">
-        <v>605400</v>
+        <v>499200</v>
       </c>
       <c r="J41" s="3">
+        <v>601600</v>
+      </c>
+      <c r="K41" s="3">
         <v>398200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>321500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>311700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>335800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>354700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>394800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>408600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>466600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>492400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>405400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>422200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>384900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>378600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>117200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>79400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>239200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>275600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>208300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>132300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>125700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>140800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>160900</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,97 +3532,103 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>190900</v>
+        <v>182300</v>
       </c>
       <c r="E43" s="3">
-        <v>220900</v>
+        <v>189700</v>
       </c>
       <c r="F43" s="3">
-        <v>222700</v>
+        <v>219500</v>
       </c>
       <c r="G43" s="3">
-        <v>206800</v>
+        <v>221300</v>
       </c>
       <c r="H43" s="3">
-        <v>194500</v>
+        <v>205500</v>
       </c>
       <c r="I43" s="3">
-        <v>171500</v>
+        <v>193300</v>
       </c>
       <c r="J43" s="3">
+        <v>170400</v>
+      </c>
+      <c r="K43" s="3">
         <v>164600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>141900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>183800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>150700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>144600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>234500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>221000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>236200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>152800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>268800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>283700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>52100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>203600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>18700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>17700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>20100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>20600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>29800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3300</v>
       </c>
-      <c r="AC43" s="3" t="s">
+      <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4400</v>
       </c>
-      <c r="AE43" s="3" t="s">
+      <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,97 +3716,103 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>37900</v>
+        <v>58900</v>
       </c>
       <c r="E45" s="3">
-        <v>41300</v>
+        <v>37700</v>
       </c>
       <c r="F45" s="3">
-        <v>36000</v>
+        <v>41000</v>
       </c>
       <c r="G45" s="3">
-        <v>44700</v>
+        <v>35800</v>
       </c>
       <c r="H45" s="3">
-        <v>50200</v>
+        <v>44400</v>
       </c>
       <c r="I45" s="3">
-        <v>37100</v>
+        <v>49900</v>
       </c>
       <c r="J45" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K45" s="3">
         <v>48900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>49400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>30600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>40000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>137400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>157900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>126800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>205300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>197200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>178300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>186600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>370700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>171500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>171900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>170900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>158600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>168700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>91700</v>
       </c>
-      <c r="AC45" s="3" t="s">
+      <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>67900</v>
       </c>
-      <c r="AE45" s="3" t="s">
+      <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3799,186 +3900,195 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>269700</v>
+        <v>317300</v>
       </c>
       <c r="E47" s="3">
-        <v>204100</v>
+        <v>268100</v>
       </c>
       <c r="F47" s="3">
-        <v>196100</v>
+        <v>202800</v>
       </c>
       <c r="G47" s="3">
-        <v>301800</v>
+        <v>194900</v>
       </c>
       <c r="H47" s="3">
-        <v>325100</v>
+        <v>299900</v>
       </c>
       <c r="I47" s="3">
-        <v>257600</v>
+        <v>323100</v>
       </c>
       <c r="J47" s="3">
+        <v>256000</v>
+      </c>
+      <c r="K47" s="3">
         <v>425000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>486500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>446600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>398400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>341000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>305200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>302800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>391500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>510400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>578100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>655400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>909100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>968300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>688300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>707400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>617000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>261900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>255800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>314900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>297700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>236800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F48" s="3">
+        <v>13700</v>
+      </c>
+      <c r="G48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="H48" s="3">
+        <v>15400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>16800</v>
+      </c>
+      <c r="J48" s="3">
+        <v>19500</v>
+      </c>
+      <c r="K48" s="3">
+        <v>25500</v>
+      </c>
+      <c r="L48" s="3">
+        <v>25700</v>
+      </c>
+      <c r="M48" s="3">
+        <v>30900</v>
+      </c>
+      <c r="N48" s="3">
+        <v>33100</v>
+      </c>
+      <c r="O48" s="3">
+        <v>36300</v>
+      </c>
+      <c r="P48" s="3">
+        <v>45200</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>56900</v>
+      </c>
+      <c r="R48" s="3">
+        <v>70100</v>
+      </c>
+      <c r="S48" s="3">
+        <v>81600</v>
+      </c>
+      <c r="T48" s="3">
+        <v>92000</v>
+      </c>
+      <c r="U48" s="3">
+        <v>98000</v>
+      </c>
+      <c r="V48" s="3">
+        <v>96100</v>
+      </c>
+      <c r="W48" s="3">
+        <v>38600</v>
+      </c>
+      <c r="X48" s="3">
         <v>14000</v>
       </c>
-      <c r="E48" s="3">
-        <v>13800</v>
-      </c>
-      <c r="F48" s="3">
-        <v>14600</v>
-      </c>
-      <c r="G48" s="3">
-        <v>15500</v>
-      </c>
-      <c r="H48" s="3">
-        <v>16900</v>
-      </c>
-      <c r="I48" s="3">
-        <v>19600</v>
-      </c>
-      <c r="J48" s="3">
-        <v>25500</v>
-      </c>
-      <c r="K48" s="3">
-        <v>25700</v>
-      </c>
-      <c r="L48" s="3">
-        <v>30900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>33100</v>
-      </c>
-      <c r="N48" s="3">
-        <v>36300</v>
-      </c>
-      <c r="O48" s="3">
-        <v>45200</v>
-      </c>
-      <c r="P48" s="3">
-        <v>56900</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>70100</v>
-      </c>
-      <c r="R48" s="3">
-        <v>81600</v>
-      </c>
-      <c r="S48" s="3">
-        <v>92000</v>
-      </c>
-      <c r="T48" s="3">
-        <v>98000</v>
-      </c>
-      <c r="U48" s="3">
-        <v>96100</v>
-      </c>
-      <c r="V48" s="3">
-        <v>38600</v>
-      </c>
-      <c r="W48" s="3">
-        <v>14000</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8900</v>
       </c>
-      <c r="AC48" s="3" t="s">
+      <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5200</v>
       </c>
-      <c r="AE48" s="3" t="s">
+      <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4176,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4268,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4360,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>31400</v>
+        <v>47100</v>
       </c>
       <c r="E52" s="3">
-        <v>15000</v>
+        <v>31200</v>
       </c>
       <c r="F52" s="3">
-        <v>20300</v>
+        <v>14900</v>
       </c>
       <c r="G52" s="3">
-        <v>24000</v>
+        <v>20200</v>
       </c>
       <c r="H52" s="3">
-        <v>21000</v>
+        <v>23900</v>
       </c>
       <c r="I52" s="3">
-        <v>20600</v>
+        <v>20900</v>
       </c>
       <c r="J52" s="3">
+        <v>20500</v>
+      </c>
+      <c r="K52" s="3">
         <v>12300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>36500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>30900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>19500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>17900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>36100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>41400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>38800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>88800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>50000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>152900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>290800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>386900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>361500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>337900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>205100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>240600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>141700</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4544,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1300000</v>
+        <v>1419900</v>
       </c>
       <c r="E54" s="3">
-        <v>1302700</v>
+        <v>1292000</v>
       </c>
       <c r="F54" s="3">
-        <v>1195600</v>
+        <v>1294700</v>
       </c>
       <c r="G54" s="3">
-        <v>1186700</v>
+        <v>1188200</v>
       </c>
       <c r="H54" s="3">
-        <v>1110300</v>
+        <v>1179300</v>
       </c>
       <c r="I54" s="3">
-        <v>1112100</v>
+        <v>1103400</v>
       </c>
       <c r="J54" s="3">
+        <v>1105200</v>
+      </c>
+      <c r="K54" s="3">
         <v>1075900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1043400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1023500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>987300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>962600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1165300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1187000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1325500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1485000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1599600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1701200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1689500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2069800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1059600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1142900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1349900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1115800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1036300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>888900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>782000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>695600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>586200</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4672,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,97 +4706,101 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E57" s="3">
         <v>5300</v>
       </c>
-      <c r="E57" s="3">
-        <v>9300</v>
-      </c>
       <c r="F57" s="3">
-        <v>2800</v>
+        <v>9200</v>
       </c>
       <c r="G57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>44600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4800</v>
-      </c>
-      <c r="X57" s="3">
-        <v>5100</v>
       </c>
       <c r="Y57" s="3">
         <v>5100</v>
       </c>
       <c r="Z57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AA57" s="3">
         <v>5000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2200</v>
       </c>
-      <c r="AC57" s="3" t="s">
+      <c r="AD57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2000</v>
       </c>
-      <c r="AE57" s="3" t="s">
+      <c r="AF57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4755,97 +4888,103 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>213900</v>
+        <v>274200</v>
       </c>
       <c r="E59" s="3">
-        <v>249200</v>
+        <v>212600</v>
       </c>
       <c r="F59" s="3">
-        <v>225200</v>
+        <v>247700</v>
       </c>
       <c r="G59" s="3">
-        <v>219400</v>
+        <v>223900</v>
       </c>
       <c r="H59" s="3">
-        <v>216800</v>
+        <v>218000</v>
       </c>
       <c r="I59" s="3">
-        <v>243700</v>
+        <v>215500</v>
       </c>
       <c r="J59" s="3">
+        <v>242200</v>
+      </c>
+      <c r="K59" s="3">
         <v>241900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>251900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>264100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>291000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>332300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>337200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>330000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>338400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>420000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>456400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>433100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>431000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1611500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>224200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>361500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>189000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>220600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>277900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>152400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>55300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>205500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>51700</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4933,8 +5072,11 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4942,38 +5084,38 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>54500</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>54500</v>
+        <v>54200</v>
       </c>
       <c r="G61" s="3">
-        <v>106800</v>
+        <v>54200</v>
       </c>
       <c r="H61" s="3">
-        <v>106800</v>
+        <v>106100</v>
       </c>
       <c r="I61" s="3">
-        <v>120900</v>
+        <v>106100</v>
       </c>
       <c r="J61" s="3">
+        <v>120100</v>
+      </c>
+      <c r="K61" s="3">
         <v>143000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>143400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>137700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>113600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>71900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5022,88 +5164,91 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>16500</v>
+        <v>16900</v>
       </c>
       <c r="E62" s="3">
-        <v>13900</v>
+        <v>16400</v>
       </c>
       <c r="F62" s="3">
-        <v>11800</v>
+        <v>13800</v>
       </c>
       <c r="G62" s="3">
-        <v>11100</v>
+        <v>11700</v>
       </c>
       <c r="H62" s="3">
         <v>11000</v>
       </c>
       <c r="I62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="J62" s="3">
         <v>11100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>22600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>31600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>33700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>41200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>51400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>63800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>70700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>81500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>92100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>90000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>8900</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
@@ -5111,8 +5256,11 @@
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5348,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5440,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5532,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>253300</v>
+        <v>302800</v>
       </c>
       <c r="E66" s="3">
-        <v>331500</v>
+        <v>251800</v>
       </c>
       <c r="F66" s="3">
-        <v>299400</v>
+        <v>329400</v>
       </c>
       <c r="G66" s="3">
-        <v>348300</v>
+        <v>297500</v>
       </c>
       <c r="H66" s="3">
-        <v>339000</v>
+        <v>346100</v>
       </c>
       <c r="I66" s="3">
-        <v>381000</v>
+        <v>336900</v>
       </c>
       <c r="J66" s="3">
+        <v>378600</v>
+      </c>
+      <c r="K66" s="3">
         <v>405700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>423200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>431800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>424600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>420000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>561000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>594000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>670600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>793700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1149400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1282900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1302400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2122600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>366300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>501700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>726100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>675100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>665900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>480400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>420000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>384400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>333000</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5660,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5750,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5842,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5934,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6026,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>335700</v>
+        <v>412500</v>
       </c>
       <c r="E72" s="3">
-        <v>258700</v>
+        <v>333600</v>
       </c>
       <c r="F72" s="3">
-        <v>185600</v>
+        <v>257100</v>
       </c>
       <c r="G72" s="3">
-        <v>126400</v>
+        <v>184400</v>
       </c>
       <c r="H72" s="3">
-        <v>59000</v>
+        <v>125600</v>
       </c>
       <c r="I72" s="3">
-        <v>26400</v>
+        <v>58600</v>
       </c>
       <c r="J72" s="3">
+        <v>26200</v>
+      </c>
+      <c r="K72" s="3">
         <v>-34500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-79800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-124900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-153100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-180600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-97000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-108100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-79200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-82100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-144200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-181100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-200200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>310400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>506800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>475500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>459100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>272300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>207200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>264700</v>
       </c>
-      <c r="AC72" s="3" t="s">
+      <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>171200</v>
       </c>
-      <c r="AE72" s="3" t="s">
+      <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6210,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6302,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6394,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1046700</v>
+        <v>1117100</v>
       </c>
       <c r="E76" s="3">
-        <v>971300</v>
+        <v>1040200</v>
       </c>
       <c r="F76" s="3">
-        <v>896200</v>
+        <v>965300</v>
       </c>
       <c r="G76" s="3">
-        <v>838400</v>
+        <v>890700</v>
       </c>
       <c r="H76" s="3">
-        <v>771200</v>
+        <v>833200</v>
       </c>
       <c r="I76" s="3">
-        <v>731100</v>
+        <v>766500</v>
       </c>
       <c r="J76" s="3">
+        <v>726600</v>
+      </c>
+      <c r="K76" s="3">
         <v>670300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>620200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>591700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>562700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>542500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>604300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>593000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>654900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>691400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>450200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>418300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>387000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-52800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>693400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>641200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>623800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>440800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>370400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>408500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>361900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>311200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>253200</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6578,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>77100</v>
+        <v>78900</v>
       </c>
       <c r="E81" s="3">
-        <v>73300</v>
+        <v>76600</v>
       </c>
       <c r="F81" s="3">
-        <v>59400</v>
+        <v>72900</v>
       </c>
       <c r="G81" s="3">
-        <v>67500</v>
+        <v>59000</v>
       </c>
       <c r="H81" s="3">
-        <v>37600</v>
+        <v>67000</v>
       </c>
       <c r="I81" s="3">
-        <v>61100</v>
+        <v>37300</v>
       </c>
       <c r="J81" s="3">
+        <v>60700</v>
+      </c>
+      <c r="K81" s="3">
         <v>46000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>44300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>28400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>25800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-80400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>62200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>35100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>24100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>56400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>143200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-19700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>27100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>76900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>66600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>45000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>39900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>51000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>55200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6803,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6695,8 +6893,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6985,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7077,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7169,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7261,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7353,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>89700</v>
+        <v>57600</v>
       </c>
       <c r="E89" s="3">
-        <v>99800</v>
+        <v>89200</v>
       </c>
       <c r="F89" s="3">
-        <v>54300</v>
+        <v>99200</v>
       </c>
       <c r="G89" s="3">
-        <v>65600</v>
+        <v>53900</v>
       </c>
       <c r="H89" s="3">
-        <v>47700</v>
+        <v>65200</v>
       </c>
       <c r="I89" s="3">
-        <v>143800</v>
+        <v>47400</v>
       </c>
       <c r="J89" s="3">
+        <v>142900</v>
+      </c>
+      <c r="K89" s="3">
         <v>26300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>44700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-20200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-31500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>81400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>13600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>181100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-51800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-100600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>149000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-20100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-191800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-48500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>189300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>51400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>78700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>82100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>121600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7481,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7351,8 +7571,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7663,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7755,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-54800</v>
+        <v>-36000</v>
       </c>
       <c r="E94" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2800</v>
       </c>
-      <c r="F94" s="3">
-        <v>107600</v>
-      </c>
       <c r="G94" s="3">
-        <v>39400</v>
+        <v>107000</v>
       </c>
       <c r="H94" s="3">
-        <v>-116100</v>
+        <v>39100</v>
       </c>
       <c r="I94" s="3">
-        <v>84000</v>
+        <v>-115400</v>
       </c>
       <c r="J94" s="3">
+        <v>83500</v>
+      </c>
+      <c r="K94" s="3">
         <v>53100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-32300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-29600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-40700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-140900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-17600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-76600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>314600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-199000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>91300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-34500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>127200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>322400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>65700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-37700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>50800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-62200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-117500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-98800</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7883,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7973,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8065,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8157,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,121 +8249,127 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-69900</v>
+        <v>45900</v>
       </c>
       <c r="E100" s="3">
-        <v>-900</v>
+        <v>-69400</v>
       </c>
       <c r="F100" s="3">
-        <v>-54600</v>
+        <v>-800</v>
       </c>
       <c r="G100" s="3">
-        <v>-7600</v>
+        <v>-54300</v>
       </c>
       <c r="H100" s="3">
-        <v>-38400</v>
+        <v>-7500</v>
       </c>
       <c r="I100" s="3">
-        <v>-22000</v>
+        <v>-38200</v>
       </c>
       <c r="J100" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-6400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>20500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>39700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>129200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>11400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-9600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-242800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-11400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>75400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-10500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-15300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>33900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-86300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-14100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>8800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
@@ -8132,146 +8380,152 @@
         <v>0</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-34600</v>
+        <v>66700</v>
       </c>
       <c r="E102" s="3">
-        <v>96200</v>
+        <v>-34400</v>
       </c>
       <c r="F102" s="3">
-        <v>107300</v>
+        <v>95600</v>
       </c>
       <c r="G102" s="3">
-        <v>97200</v>
+        <v>106600</v>
       </c>
       <c r="H102" s="3">
-        <v>-106500</v>
+        <v>96600</v>
       </c>
       <c r="I102" s="3">
-        <v>206000</v>
+        <v>-105800</v>
       </c>
       <c r="J102" s="3">
+        <v>204800</v>
+      </c>
+      <c r="K102" s="3">
         <v>73000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>19300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-39500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-43300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-29500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>85100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>31900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-63600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>149000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-231900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-111400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>75600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>81000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>49500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>12800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>15400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-7000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>YRD</t>
   </si>
@@ -656,415 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>176100</v>
+        <v>211000</v>
       </c>
       <c r="E8" s="3">
-        <v>181100</v>
+        <v>194300</v>
       </c>
       <c r="F8" s="3">
-        <v>183000</v>
+        <v>179700</v>
       </c>
       <c r="G8" s="3">
-        <v>136300</v>
+        <v>184800</v>
       </c>
       <c r="H8" s="3">
-        <v>150300</v>
+        <v>186700</v>
       </c>
       <c r="I8" s="3">
+        <v>139000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>153400</v>
+      </c>
+      <c r="K8" s="3">
         <v>116200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>208100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>141900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>170100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>159900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>156400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>166700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>142400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>105100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>149500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>388500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>316600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>345800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>302600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>431100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>317700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>418100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>540200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>270800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>224700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>175600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>148600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>155800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>127500</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>25500</v>
+        <v>34800</v>
       </c>
       <c r="E9" s="3">
-        <v>33900</v>
+        <v>32900</v>
       </c>
       <c r="F9" s="3">
-        <v>47900</v>
+        <v>26000</v>
       </c>
       <c r="G9" s="3">
-        <v>27600</v>
+        <v>34600</v>
       </c>
       <c r="H9" s="3">
-        <v>29200</v>
+        <v>48800</v>
       </c>
       <c r="I9" s="3">
+        <v>28200</v>
+      </c>
+      <c r="J9" s="3">
+        <v>29800</v>
+      </c>
+      <c r="K9" s="3">
         <v>30900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>47200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>30100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>25800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>26000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>24800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>85700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>33400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>23000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>15000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>26800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>24000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>25400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>26300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>33000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>38100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>43000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>38000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>21800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>17700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>13800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>8500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>8200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>150500</v>
+        <v>176200</v>
       </c>
       <c r="E10" s="3">
-        <v>147200</v>
+        <v>161400</v>
       </c>
       <c r="F10" s="3">
-        <v>135100</v>
+        <v>153600</v>
       </c>
       <c r="G10" s="3">
-        <v>108700</v>
+        <v>150200</v>
       </c>
       <c r="H10" s="3">
-        <v>121100</v>
+        <v>137900</v>
       </c>
       <c r="I10" s="3">
+        <v>110900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>123600</v>
+      </c>
+      <c r="K10" s="3">
         <v>85300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>160900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>111800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>144300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>134000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>131600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>81000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>109000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>82100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>134500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>361700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>292600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>320400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>276300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>398100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>279600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>375100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>502200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>249000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>207000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>161800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>140000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>147500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>120600</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1097,22 +1123,24 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>6600</v>
+        <v>7900</v>
       </c>
       <c r="E12" s="3">
-        <v>5400</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+        <v>5700</v>
+      </c>
+      <c r="F12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5500</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1189,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,52 +1315,58 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>94200</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>94200</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1340,11 +1380,11 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1373,8 +1413,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1465,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>81100</v>
+        <v>149200</v>
       </c>
       <c r="E17" s="3">
-        <v>85300</v>
+        <v>113400</v>
       </c>
       <c r="F17" s="3">
-        <v>90200</v>
+        <v>82800</v>
       </c>
       <c r="G17" s="3">
-        <v>61300</v>
+        <v>87000</v>
       </c>
       <c r="H17" s="3">
-        <v>63000</v>
+        <v>92000</v>
       </c>
       <c r="I17" s="3">
+        <v>62500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>64300</v>
+      </c>
+      <c r="K17" s="3">
         <v>69800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>138400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>96200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>112800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>119500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>119500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>248700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>126600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>141300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>147800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>286800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>281700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>319500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>267200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>295500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>341600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>406400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>455900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>191700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>168600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>120200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>91400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>98100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>94900</v>
+        <v>61800</v>
       </c>
       <c r="E18" s="3">
-        <v>95800</v>
+        <v>80900</v>
       </c>
       <c r="F18" s="3">
-        <v>92700</v>
+        <v>96900</v>
       </c>
       <c r="G18" s="3">
-        <v>75000</v>
+        <v>97800</v>
       </c>
       <c r="H18" s="3">
-        <v>87300</v>
+        <v>94600</v>
       </c>
       <c r="I18" s="3">
+        <v>76500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>89100</v>
+      </c>
+      <c r="K18" s="3">
         <v>46400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>69700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>45700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>57300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>40400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>36800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-82000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>15800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-36200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>101700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>34900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>26300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>35400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>135600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-23900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>11700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>84200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>79100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>56100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>55400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>57100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>57700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,192 +1780,206 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F20" s="3">
         <v>3500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>3200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-4100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-4800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-6100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-2700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-27000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>3300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>7400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>32700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>12300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>9300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>21400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>4700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>2000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>3900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>3700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>2000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>98400</v>
+        <v>70700</v>
       </c>
       <c r="E21" s="3">
-        <v>99000</v>
+        <v>87300</v>
       </c>
       <c r="F21" s="3">
-        <v>92200</v>
+        <v>100400</v>
       </c>
       <c r="G21" s="3">
-        <v>76200</v>
+        <v>101000</v>
       </c>
       <c r="H21" s="3">
-        <v>88200</v>
+        <v>94000</v>
       </c>
       <c r="I21" s="3">
+        <v>77800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>90000</v>
+      </c>
+      <c r="K21" s="3">
         <v>46100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>72700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>45100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>54300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>35900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>34200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-89000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>13300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-39300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>7300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>76700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>38300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>33500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>73100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>164200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-14800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>33000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>94400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>81200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>58000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>59400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>61500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>59800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1990,192 +2070,210 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>98400</v>
+        <v>70700</v>
       </c>
       <c r="E23" s="3">
-        <v>99000</v>
+        <v>87100</v>
       </c>
       <c r="F23" s="3">
-        <v>92200</v>
+        <v>100400</v>
       </c>
       <c r="G23" s="3">
-        <v>76000</v>
+        <v>101000</v>
       </c>
       <c r="H23" s="3">
-        <v>89000</v>
+        <v>94000</v>
       </c>
       <c r="I23" s="3">
+        <v>77500</v>
+      </c>
+      <c r="J23" s="3">
+        <v>90900</v>
+      </c>
+      <c r="K23" s="3">
         <v>47000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>70500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>45200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>54800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>36300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>32100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-88000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>13400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-38900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>3400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>74700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>38200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>33700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>68100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>147900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>33100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>88900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>81100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>57700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>59300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>60900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>59700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="E24" s="3">
-        <v>22400</v>
+        <v>18600</v>
       </c>
       <c r="F24" s="3">
+        <v>19900</v>
+      </c>
+      <c r="G24" s="3">
+        <v>22800</v>
+      </c>
+      <c r="H24" s="3">
+        <v>19700</v>
+      </c>
+      <c r="I24" s="3">
+        <v>17300</v>
+      </c>
+      <c r="J24" s="3">
+        <v>22500</v>
+      </c>
+      <c r="K24" s="3">
+        <v>9700</v>
+      </c>
+      <c r="L24" s="3">
+        <v>9800</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N24" s="3">
+        <v>10500</v>
+      </c>
+      <c r="O24" s="3">
+        <v>7900</v>
+      </c>
+      <c r="P24" s="3">
+        <v>6300</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="R24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S24" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="T24" s="3">
+        <v>600</v>
+      </c>
+      <c r="U24" s="3">
+        <v>12500</v>
+      </c>
+      <c r="V24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="W24" s="3">
+        <v>9700</v>
+      </c>
+      <c r="X24" s="3">
+        <v>11700</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>4700</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>14500</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>12700</v>
+      </c>
+      <c r="AE24" s="3">
         <v>19300</v>
       </c>
-      <c r="G24" s="3">
-        <v>16900</v>
-      </c>
-      <c r="H24" s="3">
-        <v>22000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>9700</v>
-      </c>
-      <c r="J24" s="3">
-        <v>9800</v>
-      </c>
-      <c r="K24" s="3">
-        <v>-700</v>
-      </c>
-      <c r="L24" s="3">
-        <v>10500</v>
-      </c>
-      <c r="M24" s="3">
-        <v>7900</v>
-      </c>
-      <c r="N24" s="3">
-        <v>6300</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="P24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="R24" s="3">
-        <v>600</v>
-      </c>
-      <c r="S24" s="3">
-        <v>12500</v>
-      </c>
-      <c r="T24" s="3">
-        <v>3100</v>
-      </c>
-      <c r="U24" s="3">
-        <v>9700</v>
-      </c>
-      <c r="V24" s="3">
-        <v>11700</v>
-      </c>
-      <c r="W24" s="3">
-        <v>4700</v>
-      </c>
-      <c r="X24" s="3">
-        <v>5100</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>6000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>12000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>14500</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>12700</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>19300</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>9900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>4500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>78900</v>
+        <v>57700</v>
       </c>
       <c r="E26" s="3">
-        <v>76600</v>
+        <v>68500</v>
       </c>
       <c r="F26" s="3">
-        <v>72900</v>
+        <v>80500</v>
       </c>
       <c r="G26" s="3">
-        <v>59000</v>
+        <v>78200</v>
       </c>
       <c r="H26" s="3">
-        <v>67000</v>
+        <v>74300</v>
       </c>
       <c r="I26" s="3">
+        <v>60200</v>
+      </c>
+      <c r="J26" s="3">
+        <v>68400</v>
+      </c>
+      <c r="K26" s="3">
         <v>37300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>60700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>46000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>44300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>28400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>25800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-80400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>11100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-32300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>62200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>35100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>24100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>56400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>143200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>27100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>76900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>66600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>45000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>39900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>51000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>55200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>78900</v>
+        <v>57700</v>
       </c>
       <c r="E27" s="3">
-        <v>76600</v>
+        <v>68500</v>
       </c>
       <c r="F27" s="3">
-        <v>72900</v>
+        <v>80500</v>
       </c>
       <c r="G27" s="3">
-        <v>59000</v>
+        <v>78200</v>
       </c>
       <c r="H27" s="3">
-        <v>67000</v>
+        <v>74300</v>
       </c>
       <c r="I27" s="3">
+        <v>60200</v>
+      </c>
+      <c r="J27" s="3">
+        <v>68400</v>
+      </c>
+      <c r="K27" s="3">
         <v>37300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>60700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>46000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>44300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>28400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>25800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-80400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>11100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-32300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>62200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>35100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>24100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>56400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>143200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>27100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>76900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>66600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>45000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>39900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>51000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>55200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2634,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,192 +2952,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-3200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>4100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>4800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>6100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>2400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>2700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>27000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-3300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-7400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-32700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-12300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-21400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>78900</v>
+        <v>57700</v>
       </c>
       <c r="E33" s="3">
-        <v>76600</v>
+        <v>68500</v>
       </c>
       <c r="F33" s="3">
-        <v>72900</v>
+        <v>80500</v>
       </c>
       <c r="G33" s="3">
-        <v>59000</v>
+        <v>78200</v>
       </c>
       <c r="H33" s="3">
-        <v>67000</v>
+        <v>74300</v>
       </c>
       <c r="I33" s="3">
+        <v>60200</v>
+      </c>
+      <c r="J33" s="3">
+        <v>68400</v>
+      </c>
+      <c r="K33" s="3">
         <v>37300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>60700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>46000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>44300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>28400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>25800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-80400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>11100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-32300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>62200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>35100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>24100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>56400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>143200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>27100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>76900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>66600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>45000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>39900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>51000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>55200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>78900</v>
+        <v>57700</v>
       </c>
       <c r="E35" s="3">
-        <v>76600</v>
+        <v>68500</v>
       </c>
       <c r="F35" s="3">
-        <v>72900</v>
+        <v>80500</v>
       </c>
       <c r="G35" s="3">
-        <v>59000</v>
+        <v>78200</v>
       </c>
       <c r="H35" s="3">
-        <v>67000</v>
+        <v>74300</v>
       </c>
       <c r="I35" s="3">
+        <v>60200</v>
+      </c>
+      <c r="J35" s="3">
+        <v>68400</v>
+      </c>
+      <c r="K35" s="3">
         <v>37300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>60700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>46000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>44300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>28400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>25800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-80400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>11100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-32300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>62200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>35100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>24100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>56400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>143200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>27100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>76900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>66600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>45000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>39900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>51000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>55200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,100 +3523,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>800100</v>
+        <v>775000</v>
       </c>
       <c r="E41" s="3">
-        <v>751300</v>
+        <v>832300</v>
       </c>
       <c r="F41" s="3">
-        <v>802500</v>
+        <v>816500</v>
       </c>
       <c r="G41" s="3">
-        <v>701500</v>
+        <v>766600</v>
       </c>
       <c r="H41" s="3">
-        <v>590200</v>
+        <v>818900</v>
       </c>
       <c r="I41" s="3">
+        <v>715800</v>
+      </c>
+      <c r="J41" s="3">
+        <v>602300</v>
+      </c>
+      <c r="K41" s="3">
         <v>499200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>601600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>398200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>321500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>311700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>335800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>354700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>394800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>408600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>466600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>492400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>405400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>422200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>384900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>378600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>117200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>79400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>239200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>275600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>208300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>132300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>125700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>140800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>160900</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3535,100 +3715,112 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>182300</v>
+        <v>341900</v>
       </c>
       <c r="E43" s="3">
-        <v>189700</v>
+        <v>193800</v>
       </c>
       <c r="F43" s="3">
-        <v>219500</v>
+        <v>186000</v>
       </c>
       <c r="G43" s="3">
-        <v>221300</v>
+        <v>193600</v>
       </c>
       <c r="H43" s="3">
-        <v>205500</v>
+        <v>224000</v>
       </c>
       <c r="I43" s="3">
+        <v>225800</v>
+      </c>
+      <c r="J43" s="3">
+        <v>209700</v>
+      </c>
+      <c r="K43" s="3">
         <v>193300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>170400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>164600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>141900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>183800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>150700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>144600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>234500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>221000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>236200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>152800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>268800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>283700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>52100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>203600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>18700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>17700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>20100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>20600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>29800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>3300</v>
-      </c>
-      <c r="AD43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>4400</v>
       </c>
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3719,100 +3911,112 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>58900</v>
+        <v>234400</v>
       </c>
       <c r="E45" s="3">
-        <v>37700</v>
+        <v>179500</v>
       </c>
       <c r="F45" s="3">
-        <v>41000</v>
+        <v>60100</v>
       </c>
       <c r="G45" s="3">
-        <v>35800</v>
+        <v>38400</v>
       </c>
       <c r="H45" s="3">
-        <v>44400</v>
+        <v>41900</v>
       </c>
       <c r="I45" s="3">
+        <v>36500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>45300</v>
+      </c>
+      <c r="K45" s="3">
         <v>49900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>36800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>48900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>49400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>30400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>30600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>40000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>137400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>157900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>126800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>205300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>197200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>178300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>186600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>370700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>171500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>171900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>170900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>158600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>168700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>91700</v>
-      </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>67900</v>
       </c>
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>67900</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3903,192 +4107,210 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>317300</v>
+        <v>266100</v>
       </c>
       <c r="E47" s="3">
-        <v>268100</v>
+        <v>308800</v>
       </c>
       <c r="F47" s="3">
-        <v>202800</v>
+        <v>323800</v>
       </c>
       <c r="G47" s="3">
-        <v>194900</v>
+        <v>273500</v>
       </c>
       <c r="H47" s="3">
-        <v>299900</v>
+        <v>207000</v>
       </c>
       <c r="I47" s="3">
+        <v>198900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>306000</v>
+      </c>
+      <c r="K47" s="3">
         <v>323100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>256000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>425000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>486500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>446600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>398400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>341000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>305200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>302800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>391500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>510400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>578100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>655400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>909100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>968300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>688300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>707400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>617000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>261900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>255800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>314900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>297700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>236800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F48" s="3">
+        <v>14500</v>
+      </c>
+      <c r="G48" s="3">
         <v>14200</v>
       </c>
-      <c r="E48" s="3">
-        <v>13900</v>
-      </c>
-      <c r="F48" s="3">
-        <v>13700</v>
-      </c>
-      <c r="G48" s="3">
-        <v>14600</v>
-      </c>
       <c r="H48" s="3">
-        <v>15400</v>
+        <v>14000</v>
       </c>
       <c r="I48" s="3">
+        <v>14800</v>
+      </c>
+      <c r="J48" s="3">
+        <v>15700</v>
+      </c>
+      <c r="K48" s="3">
         <v>16800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>19500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>25500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>25700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>30900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>33100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>36300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>45200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>56900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>70100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>81600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>92000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>98000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>96100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>38600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>14000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>13500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>11900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>12200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>12100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>8900</v>
-      </c>
-      <c r="AD48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>5200</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4179,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,100 +4597,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>47100</v>
+        <v>34700</v>
       </c>
       <c r="E52" s="3">
-        <v>31200</v>
+        <v>20900</v>
       </c>
       <c r="F52" s="3">
-        <v>14900</v>
+        <v>48000</v>
       </c>
       <c r="G52" s="3">
-        <v>20200</v>
+        <v>31900</v>
       </c>
       <c r="H52" s="3">
-        <v>23900</v>
+        <v>15200</v>
       </c>
       <c r="I52" s="3">
+        <v>20600</v>
+      </c>
+      <c r="J52" s="3">
+        <v>24400</v>
+      </c>
+      <c r="K52" s="3">
         <v>20900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>20500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>12300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>13500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>13800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>29800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>36500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>30900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>19500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>12400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>17900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>36100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>41400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>38800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>88800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>50000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>152900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>290800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>386900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>361500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>337900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>205100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>240600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>141700</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1419900</v>
+        <v>1665800</v>
       </c>
       <c r="E54" s="3">
-        <v>1292000</v>
+        <v>1549000</v>
       </c>
       <c r="F54" s="3">
-        <v>1294700</v>
+        <v>1448800</v>
       </c>
       <c r="G54" s="3">
-        <v>1188200</v>
+        <v>1318300</v>
       </c>
       <c r="H54" s="3">
-        <v>1179300</v>
+        <v>1321100</v>
       </c>
       <c r="I54" s="3">
+        <v>1212500</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1203400</v>
+      </c>
+      <c r="K54" s="3">
         <v>1103400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1105200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1075900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1043400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1023500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>987300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>962600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1165300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1187000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1325500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1485000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1599600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1701200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1689500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2069800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1059600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1142900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1349900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1115800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1036300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>888900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>782000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>695600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>586200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,100 +4967,108 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>9400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="L57" s="3">
         <v>4300</v>
       </c>
-      <c r="E57" s="3">
-        <v>5300</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="M57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="N57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="O57" s="3">
         <v>9200</v>
       </c>
-      <c r="G57" s="3">
-        <v>2700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>4300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>2700</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="S57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="T57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="U57" s="3">
+        <v>6700</v>
+      </c>
+      <c r="V57" s="3">
+        <v>9600</v>
+      </c>
+      <c r="W57" s="3">
+        <v>8400</v>
+      </c>
+      <c r="X57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>44600</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AA57" s="3">
         <v>5100</v>
       </c>
-      <c r="M57" s="3">
-        <v>9200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1800</v>
-      </c>
-      <c r="O57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="AB57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AC57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AD57" s="3">
         <v>3400</v>
       </c>
-      <c r="Q57" s="3">
-        <v>5600</v>
-      </c>
-      <c r="R57" s="3">
-        <v>5700</v>
-      </c>
-      <c r="S57" s="3">
-        <v>6700</v>
-      </c>
-      <c r="T57" s="3">
-        <v>9600</v>
-      </c>
-      <c r="U57" s="3">
-        <v>8400</v>
-      </c>
-      <c r="V57" s="3">
-        <v>8200</v>
-      </c>
-      <c r="W57" s="3">
-        <v>44600</v>
-      </c>
-      <c r="X57" s="3">
-        <v>4800</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>5100</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>5100</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>3400</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>2200</v>
-      </c>
-      <c r="AD57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>2000</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4891,100 +5159,112 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>274200</v>
+        <v>295900</v>
       </c>
       <c r="E59" s="3">
-        <v>212600</v>
+        <v>290600</v>
       </c>
       <c r="F59" s="3">
-        <v>247700</v>
+        <v>279800</v>
       </c>
       <c r="G59" s="3">
-        <v>223900</v>
+        <v>216900</v>
       </c>
       <c r="H59" s="3">
-        <v>218000</v>
+        <v>252700</v>
       </c>
       <c r="I59" s="3">
+        <v>228400</v>
+      </c>
+      <c r="J59" s="3">
+        <v>222500</v>
+      </c>
+      <c r="K59" s="3">
         <v>215500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>242200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>241900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>251900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>264100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>291000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>332300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>337200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>330000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>338400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>420000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>456400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>433100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>431000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1611500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>224200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>361500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>189000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>220600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>277900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>152400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>55300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>205500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>51700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5075,8 +5355,14 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5087,41 +5373,41 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>54200</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>54200</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>55300</v>
+      </c>
+      <c r="I61" s="3">
+        <v>55300</v>
+      </c>
+      <c r="J61" s="3">
+        <v>108300</v>
+      </c>
+      <c r="K61" s="3">
         <v>106100</v>
       </c>
-      <c r="I61" s="3">
-        <v>106100</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>120100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>143000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>143400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>137700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>113600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>71900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5167,100 +5453,112 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>16100</v>
+      </c>
+      <c r="F62" s="3">
+        <v>17200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>16700</v>
+      </c>
+      <c r="H62" s="3">
+        <v>14100</v>
+      </c>
+      <c r="I62" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>11200</v>
+      </c>
+      <c r="K62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="L62" s="3">
+        <v>11100</v>
+      </c>
+      <c r="M62" s="3">
+        <v>15600</v>
+      </c>
+      <c r="N62" s="3">
+        <v>20400</v>
+      </c>
+      <c r="O62" s="3">
         <v>16900</v>
       </c>
-      <c r="E62" s="3">
-        <v>16400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>13800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>11700</v>
-      </c>
-      <c r="H62" s="3">
-        <v>11000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>10900</v>
-      </c>
-      <c r="J62" s="3">
-        <v>11100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>15600</v>
-      </c>
-      <c r="L62" s="3">
-        <v>20400</v>
-      </c>
-      <c r="M62" s="3">
-        <v>16900</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>10800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>5600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>20900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>22600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>31600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>33700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>41200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>51400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>63800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>70700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>81500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>92100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>90000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>8900</v>
-      </c>
-      <c r="AD62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>302800</v>
+        <v>402100</v>
       </c>
       <c r="E66" s="3">
-        <v>251800</v>
+        <v>336400</v>
       </c>
       <c r="F66" s="3">
-        <v>329400</v>
+        <v>308900</v>
       </c>
       <c r="G66" s="3">
-        <v>297500</v>
+        <v>256900</v>
       </c>
       <c r="H66" s="3">
-        <v>346100</v>
+        <v>336100</v>
       </c>
       <c r="I66" s="3">
+        <v>303600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>353200</v>
+      </c>
+      <c r="K66" s="3">
         <v>336900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>378600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>405700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>423200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>431800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>424600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>420000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>561000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>594000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>670600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>793700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1149400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1282900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1302400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2122600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>366300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>501700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>726100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>675100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>665900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>480400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>420000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>384400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>333000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5937,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>412500</v>
+        <v>547000</v>
       </c>
       <c r="E72" s="3">
-        <v>333600</v>
+        <v>489300</v>
       </c>
       <c r="F72" s="3">
-        <v>257100</v>
+        <v>420900</v>
       </c>
       <c r="G72" s="3">
-        <v>184400</v>
+        <v>340400</v>
       </c>
       <c r="H72" s="3">
-        <v>125600</v>
+        <v>262400</v>
       </c>
       <c r="I72" s="3">
+        <v>188200</v>
+      </c>
+      <c r="J72" s="3">
+        <v>128100</v>
+      </c>
+      <c r="K72" s="3">
         <v>58600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>26200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-34500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-79800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-124900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-153100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-180600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-97000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-108100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-79200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-82100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-144200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-181100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-200200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>310400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>506800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>475500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>459100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>272300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>207200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>264700</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>171200</v>
       </c>
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>171200</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1117100</v>
+        <v>1263700</v>
       </c>
       <c r="E76" s="3">
-        <v>1040200</v>
+        <v>1212600</v>
       </c>
       <c r="F76" s="3">
-        <v>965300</v>
+        <v>1139900</v>
       </c>
       <c r="G76" s="3">
-        <v>890700</v>
+        <v>1061400</v>
       </c>
       <c r="H76" s="3">
-        <v>833200</v>
+        <v>985000</v>
       </c>
       <c r="I76" s="3">
+        <v>908800</v>
+      </c>
+      <c r="J76" s="3">
+        <v>850200</v>
+      </c>
+      <c r="K76" s="3">
         <v>766500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>726600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>670300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>620200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>591700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>562700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>542500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>604300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>593000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>654900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>691400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>450200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>418300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>387000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-52800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>693400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>641200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>623800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>440800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>370400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>408500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>361900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>311200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>253200</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>78900</v>
+        <v>57700</v>
       </c>
       <c r="E81" s="3">
-        <v>76600</v>
+        <v>68500</v>
       </c>
       <c r="F81" s="3">
-        <v>72900</v>
+        <v>80500</v>
       </c>
       <c r="G81" s="3">
-        <v>59000</v>
+        <v>78200</v>
       </c>
       <c r="H81" s="3">
-        <v>67000</v>
+        <v>74300</v>
       </c>
       <c r="I81" s="3">
+        <v>60200</v>
+      </c>
+      <c r="J81" s="3">
+        <v>68400</v>
+      </c>
+      <c r="K81" s="3">
         <v>37300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>60700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>46000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>44300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>28400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>25800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-80400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>11100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-32300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>62200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>35100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>24100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>56400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>143200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>27100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>76900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>66600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>45000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>39900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>51000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>55200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6896,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>57600</v>
+        <v>52000</v>
       </c>
       <c r="E89" s="3">
-        <v>89200</v>
+        <v>89100</v>
       </c>
       <c r="F89" s="3">
-        <v>99200</v>
+        <v>58800</v>
       </c>
       <c r="G89" s="3">
-        <v>53900</v>
+        <v>91000</v>
       </c>
       <c r="H89" s="3">
-        <v>65200</v>
+        <v>101200</v>
       </c>
       <c r="I89" s="3">
+        <v>55000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>66500</v>
+      </c>
+      <c r="K89" s="3">
         <v>47400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>142900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>26300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>44700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-30300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-20200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-31500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>4200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-12100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>81400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>13600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>181100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-51800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-100600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>149000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-191800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-48500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>189300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>51400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>78700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>82100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>121600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7574,8 +8016,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,100 +8212,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-36000</v>
+        <v>-75700</v>
       </c>
       <c r="E94" s="3">
-        <v>-54400</v>
+        <v>-96400</v>
       </c>
       <c r="F94" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="H94" s="3">
         <v>-2800</v>
       </c>
-      <c r="G94" s="3">
-        <v>107000</v>
-      </c>
-      <c r="H94" s="3">
-        <v>39100</v>
-      </c>
       <c r="I94" s="3">
+        <v>109200</v>
+      </c>
+      <c r="J94" s="3">
+        <v>39900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-115400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>83500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>53100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-32300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-29600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-40700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-140900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-22900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-76600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>314600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-199000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>91300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-34500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>127200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>322400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>65700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-37700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>50800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-14200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-62200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-117500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-98800</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7976,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,130 +8738,142 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>45900</v>
+        <v>-17700</v>
       </c>
       <c r="E100" s="3">
-        <v>-69400</v>
+        <v>-2100</v>
       </c>
       <c r="F100" s="3">
-        <v>-800</v>
+        <v>46800</v>
       </c>
       <c r="G100" s="3">
-        <v>-54300</v>
+        <v>-70900</v>
       </c>
       <c r="H100" s="3">
-        <v>-7500</v>
+        <v>-900</v>
       </c>
       <c r="I100" s="3">
+        <v>-55400</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-38200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-21900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-6400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>6900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>20500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>39700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>129200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>11400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>5600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-9600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-242800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>1100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-11400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>75400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-10500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-15300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>33900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-86300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-14100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>8800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
@@ -8383,149 +8881,161 @@
         <v>0</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-1300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>2200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>1100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>1300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>2500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>66700</v>
+        <v>-41600</v>
       </c>
       <c r="E102" s="3">
-        <v>-34400</v>
+        <v>-9200</v>
       </c>
       <c r="F102" s="3">
-        <v>95600</v>
+        <v>68100</v>
       </c>
       <c r="G102" s="3">
-        <v>106600</v>
+        <v>-35100</v>
       </c>
       <c r="H102" s="3">
-        <v>96600</v>
+        <v>97600</v>
       </c>
       <c r="I102" s="3">
+        <v>108800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>98600</v>
+      </c>
+      <c r="K102" s="3">
         <v>-105800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>204800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>73000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>19300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-39500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-21100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-43300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-29500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-4500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>85100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-16300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>31900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-63600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>149000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-231900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-111400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>75600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>81000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>49500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>12800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>15400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-7000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>YRD</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>211000</v>
+        <v>210900</v>
       </c>
       <c r="E8" s="3">
-        <v>194300</v>
+        <v>205900</v>
       </c>
       <c r="F8" s="3">
+        <v>190900</v>
+      </c>
+      <c r="G8" s="3">
         <v>179700</v>
       </c>
-      <c r="G8" s="3">
-        <v>184800</v>
-      </c>
       <c r="H8" s="3">
-        <v>186700</v>
+        <v>179600</v>
       </c>
       <c r="I8" s="3">
-        <v>139000</v>
+        <v>182600</v>
       </c>
       <c r="J8" s="3">
+        <v>143600</v>
+      </c>
+      <c r="K8" s="3">
         <v>153400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>116200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>208100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>141900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>170100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>159900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>156400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>166700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>142400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>105100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>149500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>388500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>316600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>345800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>302600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>431100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>317700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>418100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>540200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>270800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>224700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>175600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>148600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>155800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>127500</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>34800</v>
+        <v>29400</v>
       </c>
       <c r="E9" s="3">
-        <v>32900</v>
+        <v>33900</v>
       </c>
       <c r="F9" s="3">
+        <v>32300</v>
+      </c>
+      <c r="G9" s="3">
         <v>26000</v>
       </c>
-      <c r="G9" s="3">
-        <v>34600</v>
-      </c>
       <c r="H9" s="3">
-        <v>48800</v>
+        <v>33600</v>
       </c>
       <c r="I9" s="3">
-        <v>28200</v>
+        <v>47800</v>
       </c>
       <c r="J9" s="3">
+        <v>29100</v>
+      </c>
+      <c r="K9" s="3">
         <v>29800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>30900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>47200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>25800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>24800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>85700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>33400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>23000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>24000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>25400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>26300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>33000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>38100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>43000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>38000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>21800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>13800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>176200</v>
+        <v>181500</v>
       </c>
       <c r="E10" s="3">
-        <v>161400</v>
+        <v>172000</v>
       </c>
       <c r="F10" s="3">
-        <v>153600</v>
+        <v>158600</v>
       </c>
       <c r="G10" s="3">
-        <v>150200</v>
+        <v>153700</v>
       </c>
       <c r="H10" s="3">
-        <v>137900</v>
+        <v>146000</v>
       </c>
       <c r="I10" s="3">
-        <v>110900</v>
+        <v>134800</v>
       </c>
       <c r="J10" s="3">
+        <v>114500</v>
+      </c>
+      <c r="K10" s="3">
         <v>123600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>85300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>160900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>111800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>144300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>134000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>131600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>81000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>109000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>82100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>134500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>361700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>292600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>320400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>276300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>398100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>279600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>375100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>502200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>249000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>207000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>161800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>140000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>147500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>120600</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,31 +1138,32 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>7900</v>
+        <v>21500</v>
       </c>
       <c r="E12" s="3">
-        <v>5700</v>
+        <v>7700</v>
       </c>
       <c r="F12" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G12" s="3">
         <v>6700</v>
       </c>
-      <c r="G12" s="3">
-        <v>5500</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
+      <c r="H12" s="3">
+        <v>5300</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="J12" s="3">
+        <v>4200</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,43 +1338,46 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1365,12 +1385,12 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>94200</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1386,8 +1406,8 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1419,31 +1439,34 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>149200</v>
+        <v>123700</v>
       </c>
       <c r="E17" s="3">
-        <v>113400</v>
+        <v>107300</v>
       </c>
       <c r="F17" s="3">
+        <v>102100</v>
+      </c>
+      <c r="G17" s="3">
         <v>82800</v>
       </c>
-      <c r="G17" s="3">
-        <v>87000</v>
-      </c>
       <c r="H17" s="3">
-        <v>92000</v>
+        <v>83100</v>
       </c>
       <c r="I17" s="3">
-        <v>62500</v>
+        <v>90000</v>
       </c>
       <c r="J17" s="3">
+        <v>63800</v>
+      </c>
+      <c r="K17" s="3">
         <v>64300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>69800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>138400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>96200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>112800</v>
-      </c>
-      <c r="O17" s="3">
-        <v>119500</v>
       </c>
       <c r="P17" s="3">
         <v>119500</v>
       </c>
       <c r="Q17" s="3">
+        <v>119500</v>
+      </c>
+      <c r="R17" s="3">
         <v>248700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>126600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>141300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>147800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>286800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>281700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>319500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>267200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>295500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>341600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>406400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>455900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>191700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>168600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>120200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>91400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>98100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>61800</v>
+        <v>87200</v>
       </c>
       <c r="E18" s="3">
-        <v>80900</v>
+        <v>98700</v>
       </c>
       <c r="F18" s="3">
+        <v>88800</v>
+      </c>
+      <c r="G18" s="3">
         <v>96900</v>
       </c>
-      <c r="G18" s="3">
-        <v>97800</v>
-      </c>
       <c r="H18" s="3">
-        <v>94600</v>
+        <v>96600</v>
       </c>
       <c r="I18" s="3">
-        <v>76500</v>
+        <v>92600</v>
       </c>
       <c r="J18" s="3">
+        <v>79800</v>
+      </c>
+      <c r="K18" s="3">
         <v>89100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>46400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>69700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>45700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>57300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>40400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>36800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-82000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-36200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>101700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>34900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>26300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>35400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>135600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-23900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>84200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>79100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>56100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>55400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>57100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>57700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,227 +1815,234 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>8900</v>
+        <v>33300</v>
       </c>
       <c r="E20" s="3">
-        <v>6200</v>
+        <v>33100</v>
       </c>
       <c r="F20" s="3">
-        <v>3500</v>
+        <v>7100</v>
       </c>
       <c r="G20" s="3">
-        <v>3200</v>
+        <v>700</v>
       </c>
       <c r="H20" s="3">
-        <v>-600</v>
+        <v>1900</v>
       </c>
       <c r="I20" s="3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="J20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K20" s="3">
         <v>1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-27000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>7400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>32700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>12300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>21400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>70700</v>
+        <v>54300</v>
       </c>
       <c r="E21" s="3">
-        <v>87300</v>
+        <v>65900</v>
       </c>
       <c r="F21" s="3">
-        <v>100400</v>
+        <v>82000</v>
       </c>
       <c r="G21" s="3">
-        <v>101000</v>
+        <v>96500</v>
       </c>
       <c r="H21" s="3">
-        <v>94000</v>
+        <v>94900</v>
       </c>
       <c r="I21" s="3">
-        <v>77800</v>
+        <v>90800</v>
       </c>
       <c r="J21" s="3">
+        <v>78200</v>
+      </c>
+      <c r="K21" s="3">
         <v>90000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>46100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>72700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>45100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>54300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>35900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>34200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-89000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-39300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>76700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>38300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>33500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>73100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>164200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-14800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>33000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>94400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>81200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>58000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>59400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>61500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>59800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>70700</v>
+        <v>57000</v>
       </c>
       <c r="E23" s="3">
-        <v>87100</v>
+        <v>69000</v>
       </c>
       <c r="F23" s="3">
+        <v>85500</v>
+      </c>
+      <c r="G23" s="3">
         <v>100400</v>
       </c>
-      <c r="G23" s="3">
-        <v>101000</v>
-      </c>
       <c r="H23" s="3">
-        <v>94000</v>
+        <v>98200</v>
       </c>
       <c r="I23" s="3">
-        <v>77500</v>
+        <v>92000</v>
       </c>
       <c r="J23" s="3">
+        <v>80000</v>
+      </c>
+      <c r="K23" s="3">
         <v>90900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>47000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>70500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>45200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>54800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>36300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>32100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-88000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-38900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>74700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>38200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>33700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>68100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>147900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>33100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>88900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>81100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>57700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>59300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>60900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>59700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>13000</v>
+        <v>6400</v>
       </c>
       <c r="E24" s="3">
-        <v>18600</v>
+        <v>12700</v>
       </c>
       <c r="F24" s="3">
+        <v>18300</v>
+      </c>
+      <c r="G24" s="3">
         <v>19900</v>
       </c>
-      <c r="G24" s="3">
-        <v>22800</v>
-      </c>
       <c r="H24" s="3">
-        <v>19700</v>
+        <v>22200</v>
       </c>
       <c r="I24" s="3">
-        <v>17300</v>
+        <v>19300</v>
       </c>
       <c r="J24" s="3">
+        <v>17900</v>
+      </c>
+      <c r="K24" s="3">
         <v>22500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-7700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-6600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>11700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>12000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>14500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>12700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>19300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>9900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>57700</v>
+        <v>50700</v>
       </c>
       <c r="E26" s="3">
-        <v>68500</v>
+        <v>56400</v>
       </c>
       <c r="F26" s="3">
-        <v>80500</v>
+        <v>67300</v>
       </c>
       <c r="G26" s="3">
-        <v>78200</v>
+        <v>80600</v>
       </c>
       <c r="H26" s="3">
-        <v>74300</v>
+        <v>76000</v>
       </c>
       <c r="I26" s="3">
-        <v>60200</v>
+        <v>72700</v>
       </c>
       <c r="J26" s="3">
+        <v>62200</v>
+      </c>
+      <c r="K26" s="3">
         <v>68400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>37300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>60700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>46000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>44300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>28400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>25800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-80400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>11100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-32300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>62200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>35100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>24100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>56400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>143200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>27100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>76900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>66600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>45000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>39900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>51000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>55200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>57700</v>
+        <v>50700</v>
       </c>
       <c r="E27" s="3">
-        <v>68500</v>
+        <v>56400</v>
       </c>
       <c r="F27" s="3">
-        <v>80500</v>
+        <v>67300</v>
       </c>
       <c r="G27" s="3">
-        <v>78200</v>
+        <v>80600</v>
       </c>
       <c r="H27" s="3">
-        <v>74300</v>
+        <v>76000</v>
       </c>
       <c r="I27" s="3">
-        <v>60200</v>
+        <v>72700</v>
       </c>
       <c r="J27" s="3">
+        <v>62200</v>
+      </c>
+      <c r="K27" s="3">
         <v>68400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>37300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>60700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>46000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>44300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>28400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>25800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-80400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-32300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>62200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>35100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>24100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>56400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>143200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>27100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>76900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>66600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>45000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>39900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>51000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>55200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-8900</v>
+        <v>-33300</v>
       </c>
       <c r="E32" s="3">
-        <v>-6200</v>
+        <v>-33100</v>
       </c>
       <c r="F32" s="3">
-        <v>-3500</v>
+        <v>-7100</v>
       </c>
       <c r="G32" s="3">
-        <v>-3200</v>
+        <v>-700</v>
       </c>
       <c r="H32" s="3">
-        <v>600</v>
+        <v>-1900</v>
       </c>
       <c r="I32" s="3">
-        <v>-1000</v>
+        <v>-2000</v>
       </c>
       <c r="J32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>27000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-7400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-32700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-12300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-21400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>57700</v>
+        <v>50700</v>
       </c>
       <c r="E33" s="3">
-        <v>68500</v>
+        <v>56400</v>
       </c>
       <c r="F33" s="3">
-        <v>80500</v>
+        <v>67300</v>
       </c>
       <c r="G33" s="3">
-        <v>78200</v>
+        <v>80600</v>
       </c>
       <c r="H33" s="3">
-        <v>74300</v>
+        <v>76000</v>
       </c>
       <c r="I33" s="3">
-        <v>60200</v>
+        <v>72700</v>
       </c>
       <c r="J33" s="3">
+        <v>62200</v>
+      </c>
+      <c r="K33" s="3">
         <v>68400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>37300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>60700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>46000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>44300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>28400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>25800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-80400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-32300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>62200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>35100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>24100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>56400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>143200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>27100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>76900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>66600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>45000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>39900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>51000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>55200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>57700</v>
+        <v>50700</v>
       </c>
       <c r="E35" s="3">
-        <v>68500</v>
+        <v>56400</v>
       </c>
       <c r="F35" s="3">
-        <v>80500</v>
+        <v>67300</v>
       </c>
       <c r="G35" s="3">
-        <v>78200</v>
+        <v>80600</v>
       </c>
       <c r="H35" s="3">
-        <v>74300</v>
+        <v>76000</v>
       </c>
       <c r="I35" s="3">
-        <v>60200</v>
+        <v>72700</v>
       </c>
       <c r="J35" s="3">
+        <v>62200</v>
+      </c>
+      <c r="K35" s="3">
         <v>68400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>37300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>60700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>46000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>44300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>28400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>25800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-80400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-32300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>62200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>35100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>24100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>56400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>143200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>27100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>76900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>66600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>45000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>39900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>51000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>55200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,123 +3611,127 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>775000</v>
+        <v>528300</v>
       </c>
       <c r="E41" s="3">
-        <v>832300</v>
+        <v>756400</v>
       </c>
       <c r="F41" s="3">
-        <v>816500</v>
+        <v>817700</v>
       </c>
       <c r="G41" s="3">
-        <v>766600</v>
+        <v>816700</v>
       </c>
       <c r="H41" s="3">
-        <v>818900</v>
+        <v>745300</v>
       </c>
       <c r="I41" s="3">
-        <v>715800</v>
+        <v>801000</v>
       </c>
       <c r="J41" s="3">
+        <v>739100</v>
+      </c>
+      <c r="K41" s="3">
         <v>602300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>499200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>601600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>398200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>321500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>311700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>335800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>354700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>394800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>408600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>466600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>492400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>405400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>422200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>384900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>378600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>117200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>79400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>239200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>275600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>208300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>132300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>125700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>140800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>160900</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -3721,129 +3811,135 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>341900</v>
+        <v>765200</v>
       </c>
       <c r="E43" s="3">
-        <v>193800</v>
+        <v>499600</v>
       </c>
       <c r="F43" s="3">
-        <v>186000</v>
+        <v>423800</v>
       </c>
       <c r="G43" s="3">
-        <v>193600</v>
+        <v>418700</v>
       </c>
       <c r="H43" s="3">
-        <v>224000</v>
+        <v>397000</v>
       </c>
       <c r="I43" s="3">
-        <v>225800</v>
+        <v>406600</v>
       </c>
       <c r="J43" s="3">
+        <v>401600</v>
+      </c>
+      <c r="K43" s="3">
         <v>209700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>193300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>170400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>164600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>141900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>183800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>150700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>144600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>234500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>221000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>236200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>152800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>268800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>283700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>52100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>203600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>18700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>17700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>20100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>20600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>29800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3300</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH43" s="3">
         <v>4400</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3917,129 +4013,135 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>234400</v>
+        <v>55800</v>
       </c>
       <c r="E45" s="3">
-        <v>179500</v>
+        <v>35900</v>
       </c>
       <c r="F45" s="3">
-        <v>60100</v>
+        <v>5100</v>
       </c>
       <c r="G45" s="3">
-        <v>38400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>41900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>36500</v>
-      </c>
-      <c r="J45" s="3">
+        <v>28700</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>45300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>49900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>36800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>48900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>49400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>30600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>40000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>137400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>157900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>126800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>205300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>197200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>178300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>186600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>370700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>171500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>171900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>170900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>158600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>168700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>91700</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH45" s="3">
         <v>67900</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>1707100</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>1560000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>1446100</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>1361200</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>1208700</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>1250700</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1186400</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4113,204 +4215,213 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>266100</v>
+        <v>47600</v>
       </c>
       <c r="E47" s="3">
-        <v>308800</v>
+        <v>46400</v>
       </c>
       <c r="F47" s="3">
-        <v>323800</v>
+        <v>54000</v>
       </c>
       <c r="G47" s="3">
-        <v>273500</v>
+        <v>63300</v>
       </c>
       <c r="H47" s="3">
-        <v>207000</v>
+        <v>47000</v>
       </c>
       <c r="I47" s="3">
-        <v>198900</v>
+        <v>14900</v>
       </c>
       <c r="J47" s="3">
+        <v>37000</v>
+      </c>
+      <c r="K47" s="3">
         <v>306000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>323100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>256000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>425000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>486500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>446600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>398400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>341000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>305200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>302800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>391500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>510400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>578100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>655400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>909100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>968300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>688300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>707400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>617000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>261900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>255800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>314900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>297700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>236800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="G48" s="3">
+        <v>14500</v>
+      </c>
+      <c r="H48" s="3">
+        <v>13800</v>
+      </c>
+      <c r="I48" s="3">
         <v>13700</v>
       </c>
-      <c r="E48" s="3">
-        <v>13600</v>
-      </c>
-      <c r="F48" s="3">
-        <v>14500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>14200</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K48" s="3">
+        <v>15700</v>
+      </c>
+      <c r="L48" s="3">
+        <v>16800</v>
+      </c>
+      <c r="M48" s="3">
+        <v>19500</v>
+      </c>
+      <c r="N48" s="3">
+        <v>25500</v>
+      </c>
+      <c r="O48" s="3">
+        <v>25700</v>
+      </c>
+      <c r="P48" s="3">
+        <v>30900</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>33100</v>
+      </c>
+      <c r="R48" s="3">
+        <v>36300</v>
+      </c>
+      <c r="S48" s="3">
+        <v>45200</v>
+      </c>
+      <c r="T48" s="3">
+        <v>56900</v>
+      </c>
+      <c r="U48" s="3">
+        <v>70100</v>
+      </c>
+      <c r="V48" s="3">
+        <v>81600</v>
+      </c>
+      <c r="W48" s="3">
+        <v>92000</v>
+      </c>
+      <c r="X48" s="3">
+        <v>98000</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>96100</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>38600</v>
+      </c>
+      <c r="AA48" s="3">
         <v>14000</v>
       </c>
-      <c r="I48" s="3">
-        <v>14800</v>
-      </c>
-      <c r="J48" s="3">
-        <v>15700</v>
-      </c>
-      <c r="K48" s="3">
-        <v>16800</v>
-      </c>
-      <c r="L48" s="3">
-        <v>19500</v>
-      </c>
-      <c r="M48" s="3">
-        <v>25500</v>
-      </c>
-      <c r="N48" s="3">
-        <v>25700</v>
-      </c>
-      <c r="O48" s="3">
-        <v>30900</v>
-      </c>
-      <c r="P48" s="3">
-        <v>33100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>36300</v>
-      </c>
-      <c r="R48" s="3">
-        <v>45200</v>
-      </c>
-      <c r="S48" s="3">
-        <v>56900</v>
-      </c>
-      <c r="T48" s="3">
-        <v>70100</v>
-      </c>
-      <c r="U48" s="3">
-        <v>81600</v>
-      </c>
-      <c r="V48" s="3">
-        <v>92000</v>
-      </c>
-      <c r="W48" s="3">
-        <v>98000</v>
-      </c>
-      <c r="X48" s="3">
-        <v>96100</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>38600</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>14000</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8900</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH48" s="3">
         <v>5200</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>34700</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
+        <v>24400</v>
+      </c>
+      <c r="L52" s="3">
         <v>20900</v>
       </c>
-      <c r="F52" s="3">
-        <v>48000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>31900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>20600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>24400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>20900</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>20500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>36500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>19500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>36100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>41400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>38800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>88800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>50000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>152900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>290800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>386900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>361500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>337900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>205100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>240600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>141700</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1665800</v>
+        <v>1776000</v>
       </c>
       <c r="E54" s="3">
-        <v>1549000</v>
+        <v>1626000</v>
       </c>
       <c r="F54" s="3">
-        <v>1448800</v>
+        <v>1521600</v>
       </c>
       <c r="G54" s="3">
-        <v>1318300</v>
+        <v>1449300</v>
       </c>
       <c r="H54" s="3">
-        <v>1321100</v>
+        <v>1281600</v>
       </c>
       <c r="I54" s="3">
-        <v>1212500</v>
+        <v>1292100</v>
       </c>
       <c r="J54" s="3">
+        <v>1252000</v>
+      </c>
+      <c r="K54" s="3">
         <v>1203400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1103400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1105200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1075900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1043400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1023500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>987300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>962600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1165300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1187000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1325500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1485000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1599600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1701200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1689500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2069800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1059600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1142900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1349900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1115800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1036300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>888900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>782000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>695600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>586200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,106 +5099,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="G57" s="3">
         <v>6200</v>
       </c>
-      <c r="E57" s="3">
-        <v>5800</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I57" s="3">
+        <v>9200</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L57" s="3">
         <v>4400</v>
       </c>
-      <c r="G57" s="3">
-        <v>5400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>9400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>4400</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>44600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4800</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>5100</v>
       </c>
       <c r="AB57" s="3">
         <v>5100</v>
       </c>
       <c r="AC57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AD57" s="3">
         <v>5000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2200</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH57" s="3">
         <v>2000</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5082,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>46700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>36100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5165,129 +5299,135 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>295900</v>
+        <v>13800</v>
       </c>
       <c r="E59" s="3">
-        <v>290600</v>
+        <v>300</v>
       </c>
       <c r="F59" s="3">
-        <v>279800</v>
+        <v>200</v>
       </c>
       <c r="G59" s="3">
-        <v>216900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>252700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>228400</v>
-      </c>
-      <c r="J59" s="3">
+        <v>153700</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>222500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>215500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>242200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>241900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>251900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>264100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>291000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>332300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>337200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>330000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>338400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>420000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>456400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>433100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>431000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1611500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>224200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>361500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>189000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>220600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>277900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>152400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>55300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>205500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>51700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>258200</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>244000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>226800</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>203600</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>212300</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>252700</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>234400</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5361,56 +5501,59 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H61" s="3">
-        <v>55300</v>
+        <v>3800</v>
       </c>
       <c r="I61" s="3">
-        <v>55300</v>
+        <v>57800</v>
       </c>
       <c r="J61" s="3">
+        <v>61500</v>
+      </c>
+      <c r="K61" s="3">
         <v>108300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>106100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>120100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>143000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>143400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>137700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>113600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>71900</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -5459,106 +5602,112 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7800</v>
+        <v>187000</v>
       </c>
       <c r="E62" s="3">
-        <v>16100</v>
+        <v>132800</v>
       </c>
       <c r="F62" s="3">
-        <v>17200</v>
+        <v>78700</v>
       </c>
       <c r="G62" s="3">
-        <v>16700</v>
+        <v>79900</v>
       </c>
       <c r="H62" s="3">
-        <v>14100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>12000</v>
-      </c>
-      <c r="J62" s="3">
+        <v>13700</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>11200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>22600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>31600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>33700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>41200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>51400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>63800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>70700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>81500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>92100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>90000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8900</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>402100</v>
+        <v>452400</v>
       </c>
       <c r="E66" s="3">
-        <v>336400</v>
+        <v>392400</v>
       </c>
       <c r="F66" s="3">
-        <v>308900</v>
+        <v>330400</v>
       </c>
       <c r="G66" s="3">
-        <v>256900</v>
+        <v>309000</v>
       </c>
       <c r="H66" s="3">
-        <v>336100</v>
+        <v>249700</v>
       </c>
       <c r="I66" s="3">
-        <v>303600</v>
+        <v>328700</v>
       </c>
       <c r="J66" s="3">
+        <v>313500</v>
+      </c>
+      <c r="K66" s="3">
         <v>353200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>336900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>378600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>405700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>423200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>431800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>424600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>420000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>561000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>594000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>670600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>793700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1149400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1282900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1302400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2122600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>366300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>501700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>726100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>675100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>665900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>480400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>420000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>384400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>333000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>547000</v>
+        <v>602400</v>
       </c>
       <c r="E72" s="3">
-        <v>489300</v>
+        <v>533900</v>
       </c>
       <c r="F72" s="3">
-        <v>420900</v>
+        <v>480700</v>
       </c>
       <c r="G72" s="3">
-        <v>340400</v>
+        <v>421000</v>
       </c>
       <c r="H72" s="3">
-        <v>262400</v>
+        <v>330900</v>
       </c>
       <c r="I72" s="3">
-        <v>188200</v>
+        <v>256600</v>
       </c>
       <c r="J72" s="3">
+        <v>194300</v>
+      </c>
+      <c r="K72" s="3">
         <v>128100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>58600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>26200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-34500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-79800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-124900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-153100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-180600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-97000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-108100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-79200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-82100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-144200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-181100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-200200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>310400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>506800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>475500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>459100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>272300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>207200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>264700</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH72" s="3">
         <v>171200</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1263700</v>
+        <v>1323700</v>
       </c>
       <c r="E76" s="3">
-        <v>1212600</v>
+        <v>1233500</v>
       </c>
       <c r="F76" s="3">
-        <v>1139900</v>
+        <v>1191200</v>
       </c>
       <c r="G76" s="3">
-        <v>1061400</v>
+        <v>1140300</v>
       </c>
       <c r="H76" s="3">
-        <v>985000</v>
+        <v>1031900</v>
       </c>
       <c r="I76" s="3">
-        <v>908800</v>
+        <v>963400</v>
       </c>
       <c r="J76" s="3">
+        <v>938500</v>
+      </c>
+      <c r="K76" s="3">
         <v>850200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>766500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>726600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>670300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>620200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>591700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>562700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>542500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>604300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>593000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>654900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>691400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>450200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>418300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>387000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-52800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>693400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>641200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>623800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>440800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>370400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>408500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>361900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>311200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>253200</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>57700</v>
+        <v>50700</v>
       </c>
       <c r="E81" s="3">
-        <v>68500</v>
+        <v>56400</v>
       </c>
       <c r="F81" s="3">
-        <v>80500</v>
+        <v>67300</v>
       </c>
       <c r="G81" s="3">
-        <v>78200</v>
+        <v>80600</v>
       </c>
       <c r="H81" s="3">
-        <v>74300</v>
+        <v>76000</v>
       </c>
       <c r="I81" s="3">
-        <v>60200</v>
+        <v>72700</v>
       </c>
       <c r="J81" s="3">
+        <v>62200</v>
+      </c>
+      <c r="K81" s="3">
         <v>68400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>37300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>60700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>46000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>44300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>28400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>25800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-80400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-32300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>62200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>35100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>24100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>56400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>143200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>27100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>76900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>66600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>45000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>39900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>51000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>55200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,31 +7400,32 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>52000</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E89" s="3">
-        <v>89100</v>
+        <v>50800</v>
       </c>
       <c r="F89" s="3">
-        <v>58800</v>
-      </c>
-      <c r="G89" s="3">
-        <v>91000</v>
-      </c>
-      <c r="H89" s="3">
-        <v>101200</v>
+        <v>87500</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I89" s="3">
-        <v>55000</v>
+        <v>99000</v>
       </c>
       <c r="J89" s="3">
+        <v>56800</v>
+      </c>
+      <c r="K89" s="3">
         <v>66500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>47400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>142900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>26300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>44700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-30300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-31500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-12100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>81400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>13600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>181100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-51800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-100600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>149000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-20100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-191800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-48500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>189300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>51400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>78700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>82100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>121600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,31 +8144,32 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-75700</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E94" s="3">
-        <v>-96400</v>
+        <v>-73900</v>
       </c>
       <c r="F94" s="3">
-        <v>-36700</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-55500</v>
-      </c>
-      <c r="H94" s="3">
+        <v>-94700</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2800</v>
       </c>
-      <c r="I94" s="3">
-        <v>109200</v>
-      </c>
       <c r="J94" s="3">
+        <v>112700</v>
+      </c>
+      <c r="K94" s="3">
         <v>39900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-115400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>83500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>53100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-32300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-29600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-140900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-17600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-22900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-76600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>314600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-199000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>91300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-34500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>127200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>322400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>65700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-37700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>50800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-14200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-62200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-117500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-98800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,31 +8585,32 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-17700</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E100" s="3">
-        <v>-2100</v>
+        <v>-17300</v>
       </c>
       <c r="F100" s="3">
-        <v>46800</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-70900</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-900</v>
+        <v>-2000</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I100" s="3">
-        <v>-55400</v>
+        <v>-800</v>
       </c>
       <c r="J100" s="3">
+        <v>-57200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-7700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-38200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-21900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>20500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>39700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>129200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>11400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-9600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-242800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-11400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>75400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>33900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-86300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-14100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-6500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>8800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H101" s="3">
+        <v>300</v>
+      </c>
+      <c r="I101" s="3">
+        <v>200</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L101" s="3">
+        <v>300</v>
+      </c>
+      <c r="M101" s="3">
+        <v>200</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="S101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G101" s="3">
-        <v>300</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K101" s="3">
-        <v>300</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="V101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W101" s="3">
+        <v>500</v>
+      </c>
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="Y101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="AH101" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AI101" s="3">
         <v>200</v>
       </c>
-      <c r="U101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="V101" s="3">
-        <v>500</v>
-      </c>
-      <c r="W101" s="3">
-        <v>200</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>2200</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-41600</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-9200</v>
+        <v>-40600</v>
       </c>
       <c r="F102" s="3">
-        <v>68100</v>
+        <v>-9100</v>
       </c>
       <c r="G102" s="3">
-        <v>-35100</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>97600</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>108800</v>
+        <v>95500</v>
       </c>
       <c r="J102" s="3">
+        <v>112300</v>
+      </c>
+      <c r="K102" s="3">
         <v>98600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-105800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>204800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>73000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-39500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-43300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-29500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>85100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-16300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>31900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-63600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>149000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-231900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-111400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>75600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>81000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>49500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>12800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>15400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-7000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>YRD</t>
   </si>
@@ -656,454 +656,466 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>199000</v>
+      </c>
+      <c r="E8" s="3">
         <v>210900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>205900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>190900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>179700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>179600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>182600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>143600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>153400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>116200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>208100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>141900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>170100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>159900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>156400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>166700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>142400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>105100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>149500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>388500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>316600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>345800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>302600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>431100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>317700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>418100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>540200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>270800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>224700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>175600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>148600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>155800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>127500</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E9" s="3">
         <v>29400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>33900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>32300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>26000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>33600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>47800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>29100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>29800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>47200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>30100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>25800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>24800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>85700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>33400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>23000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>26800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>24000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>25400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>26300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>33000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>38100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>43000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>38000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>21800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>17700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>13800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>171900</v>
+      </c>
+      <c r="E10" s="3">
         <v>181500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>172000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>158600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>153700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>146000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>134800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>114500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>123600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>85300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>160900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>111800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>144300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>134000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>131600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>81000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>109000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>82100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>134500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>361700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>292600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>320400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>276300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>398100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>279600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>375100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>502200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>249000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>207000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>161800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>140000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>147500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>120600</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,35 +1151,36 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E12" s="3">
         <v>21500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5300</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>4200</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1253,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1357,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1367,20 +1386,20 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1388,12 +1407,12 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>94200</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1409,8 +1428,8 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1442,13 +1461,16 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
@@ -1460,17 +1482,17 @@
         <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>200</v>
       </c>
       <c r="J15" s="3">
+        <v>200</v>
+      </c>
+      <c r="K15" s="3">
         <v>300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1543,8 +1565,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1602,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>124100</v>
+      </c>
+      <c r="E17" s="3">
         <v>123700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>107300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>102100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>82800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>83100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>90000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>63800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>64300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>69800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>138400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>96200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>112800</v>
-      </c>
-      <c r="P17" s="3">
-        <v>119500</v>
       </c>
       <c r="Q17" s="3">
         <v>119500</v>
       </c>
       <c r="R17" s="3">
+        <v>119500</v>
+      </c>
+      <c r="S17" s="3">
         <v>248700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>126600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>141300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>147800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>286800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>281700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>319500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>267200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>295500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>341600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>406400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>455900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>191700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>168600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>120200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>91400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>98100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E18" s="3">
         <v>87200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>98700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>88800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>96900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>96600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>92600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>79800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>89100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>46400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>69700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>45700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>57300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>40400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>36800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-82000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-36200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>101700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>34900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>26300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>35400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>135600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-23900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>84200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>79100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>56100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>55400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>57100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>57700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,210 +1848,217 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E20" s="3">
         <v>33300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>33100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-27000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>7400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>32700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>12300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>21400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E21" s="3">
         <v>54300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>65900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>82000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>96500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>94900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>90800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>78200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>90000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>46100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>72700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>45100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>54300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>35900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>34200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-89000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-39300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>76700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>38300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>33500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>73100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>164200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-14800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>33000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>94400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>81200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>58000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>59400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>61500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>59800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2044,8 +2083,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2119,210 +2158,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E23" s="3">
         <v>57000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>69000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>85500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>100400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>98200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>92000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>80000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>90900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>47000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>70500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>45200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>54800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>36300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>32100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-88000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>13400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-38900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>74700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>38200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>33700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>68100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>147900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>33100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>88900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>81100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>57700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>59300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>60900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>59700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E24" s="3">
         <v>6400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>18300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>19900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>22200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>19300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>22500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-7700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-6600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>12500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>11700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>12000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>14500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>12700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>19300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>9900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2470,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E26" s="3">
         <v>50700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>56400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>67300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>80600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>76000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>72700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>62200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>68400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>60700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>46000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>44300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>28400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>25800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-80400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>11100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-32300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>62200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>35100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>24100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>56400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>143200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-19700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>27100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>76900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>66600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>45000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>39900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>51000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>55200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E27" s="3">
         <v>50700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>56400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>67300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>80600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>76000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>72700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>62200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>68400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>60700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>46000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>44300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>28400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>25800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-80400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>11100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-32300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>62200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>35100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>24100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>56400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>143200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-19700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>27100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>76900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>66600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>45000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>39900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>51000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>55200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2782,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2886,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2990,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3094,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-33300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-33100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>27000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-32700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-21400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E33" s="3">
         <v>50700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>56400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>67300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>80600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>76000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>72700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>62200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>68400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>37300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>60700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>46000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>44300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>28400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>25800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-80400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>11100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-32300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>62200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>35100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>24100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>56400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>143200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-19700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>27100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>76900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>66600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>45000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>39900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>51000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>55200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3406,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E35" s="3">
         <v>50700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>56400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>67300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>80600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>76000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>72700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>62200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>68400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>37300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>60700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>46000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>44300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>28400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>25800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-80400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>11100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-32300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>62200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>35100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>24100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>56400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>143200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-19700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>27100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>76900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>66600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>45000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>39900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>51000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>55200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3659,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,130 +3697,134 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>526300</v>
+      </c>
+      <c r="E41" s="3">
         <v>528300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>756400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>817700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>816700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>745300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>801000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>739100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>602300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>499200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>601600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>398200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>321500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>311700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>335800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>354700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>394800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>408600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>466600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>492400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>405400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>422200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>384900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>378600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>117200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>79400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>239200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>275600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>208300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>132300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>125700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>140800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>160900</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E42" s="3">
         <v>9000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>57000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10200</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -3814,109 +3903,115 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>740200</v>
+      </c>
+      <c r="E43" s="3">
         <v>765200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>499600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>423800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>418700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>397000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>406600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>401600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>209700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>193300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>170400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>164600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>141900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>183800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>150700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>144600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>234500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>221000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>236200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>152800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>268800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>283700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>52100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>203600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>18700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>17700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>20100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>20600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>29800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3300</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH43" s="3">
+      <c r="AH43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI43" s="3">
         <v>4400</v>
       </c>
-      <c r="AI43" s="3" t="s">
+      <c r="AJ43" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3941,8 +4036,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4016,136 +4111,142 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E45" s="3">
         <v>55800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>35900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28700</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>45300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>49900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>36800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>48900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>49400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>30400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>30600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>40000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>137400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>157900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>126800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>205300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>197200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>178300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>186600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>370700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>171500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>171900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>170900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>158600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>168700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>91700</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH45" s="3">
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI45" s="3">
         <v>67900</v>
       </c>
-      <c r="AI45" s="3" t="s">
+      <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1701200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1707100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1560000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1446100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1361200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1208700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1250700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1186400</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4218,210 +4319,219 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E47" s="3">
         <v>47600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>46400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>54000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>63300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>47000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>37000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>306000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>323100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>256000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>425000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>486500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>446600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>398400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>341000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>305200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>302800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>391500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>510400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>578100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>655400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>909100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>968300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>688300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>707400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>617000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>261900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>255800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>314900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>297700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>236800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E48" s="3">
         <v>13500</v>
-      </c>
-      <c r="E48" s="3">
-        <v>13400</v>
       </c>
       <c r="F48" s="3">
         <v>13400</v>
       </c>
       <c r="G48" s="3">
+        <v>13400</v>
+      </c>
+      <c r="H48" s="3">
         <v>14500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>33100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>36300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>45200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>56900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>70100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>81600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>92000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>98000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>96100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>38600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>14000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>8900</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH48" s="3">
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI48" s="3">
         <v>5200</v>
       </c>
-      <c r="AI48" s="3" t="s">
+      <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4631,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4735,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,8 +4839,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4749,83 +4868,86 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>24400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>20900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>36500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>30900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>19500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>36100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>41400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>38800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>88800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>50000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>152900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>290800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>386900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>361500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>337900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>205100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>240600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>141700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5047,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1778700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1776000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1626000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1521600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1449300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1281600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1292100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1252000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1203400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1103400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1105200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1075900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1043400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1023500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>987300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>962600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1165300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1187000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1325500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1485000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1599600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1701200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1689500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2069800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1059600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1142900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1349900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1115800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1036300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>888900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>782000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>695600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>586200</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5191,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,109 +5229,113 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E57" s="3">
         <v>6100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>8200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>44600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4800</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>5100</v>
       </c>
       <c r="AC57" s="3">
         <v>5100</v>
       </c>
       <c r="AD57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AE57" s="3">
         <v>5000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2200</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AH57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI57" s="3">
         <v>2000</v>
       </c>
-      <c r="AI57" s="3" t="s">
+      <c r="AJ57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5216,20 +5349,20 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>2700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>46700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>36100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5302,136 +5435,142 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E59" s="3">
         <v>13800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>153700</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>222500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>215500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>242200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>241900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>251900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>264100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>291000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>332300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>337200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>330000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>338400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>420000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>456400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>433100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>431000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1611500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>224200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>361500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>189000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>220600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>277900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>152400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>55300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>205500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>51700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>245900</v>
+      </c>
+      <c r="E60" s="3">
         <v>258200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>244000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>226800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>203600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>212300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>252700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>234400</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5504,59 +5643,62 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>57800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>61500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>108300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>106100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>120100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>143000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>143400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>137700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>113600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>71900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -5605,109 +5747,115 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>212900</v>
+      </c>
+      <c r="E62" s="3">
         <v>187000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>132800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>78700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>79900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13700</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>11200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>22600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>31600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>33700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>41200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>51400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>63800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>70700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>81500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>92100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>90000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>8900</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5955,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6059,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6163,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>471300</v>
+      </c>
+      <c r="E66" s="3">
         <v>452400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>392400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>330400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>309000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>249700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>328700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>313500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>353200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>336900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>378600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>405700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>423200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>431800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>424600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>420000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>561000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>594000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>670600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>793700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1149400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1282900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1302400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2122600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>366300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>501700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>726100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>675100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>665900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>480400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>420000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>384400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>333000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6307,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6409,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6513,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6617,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6721,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>607600</v>
+      </c>
+      <c r="E72" s="3">
         <v>602400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>533900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>480700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>421000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>330900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>256600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>194300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>128100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>58600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>26200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-34500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-79800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-124900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-153100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-180600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-97000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-108100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-79200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-82100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-144200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-181100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-200200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>310400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>506800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>475500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>459100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>272300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>207200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>264700</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI72" s="3">
         <v>171200</v>
       </c>
-      <c r="AI72" s="3" t="s">
+      <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6929,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7033,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7137,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1307300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1323700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1233500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1191200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1140300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1031900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>963400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>938500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>850200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>766500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>726600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>670300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>620200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>591700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>562700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>542500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>604300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>593000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>654900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>691400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>450200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>418300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>387000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-52800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>693400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>641200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>623800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>440800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>370400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>408500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>361900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>311200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>253200</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7345,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E81" s="3">
         <v>50700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>56400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>67300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>80600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>76000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>72700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>62200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>68400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>37300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>60700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>46000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>44300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>28400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>25800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-80400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>11100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-32300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>62200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>35100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>24100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>56400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>143200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-19700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>27100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>76900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>66600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>45000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>39900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>51000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>55200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,35 +7598,36 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1000</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -7502,8 +7700,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7804,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7908,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8012,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8116,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8220,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3">
         <v>50800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>87500</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3">
         <v>99000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>56800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>66500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>47400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>142900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>44700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-30300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-20200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-31500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-12100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>81400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>13600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>181100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-51800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-100600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>149000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-20100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-191800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-48500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>189300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>51400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>78700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>82100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>121600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,8 +8364,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8171,8 +8391,8 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8246,8 +8466,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8570,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8674,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
         <v>-73900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-94700</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3">
         <v>-2800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>112700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>39900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-115400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>83500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>53100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-32300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-29600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-40700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-140900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-17600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-22900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-76600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>314600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-199000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>91300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-34500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>127200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>322400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>65700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-37700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>50800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-14200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-62200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-117500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-98800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8818,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8612,8 +8845,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8687,8 +8920,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9024,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9128,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,145 +9232,151 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3">
         <v>-17300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-57200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-38200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-21900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>6900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>20500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>39700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>129200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>11400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-9600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-242800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>75400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>33900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-86300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-14100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-6500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>8800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
@@ -9139,158 +9387,164 @@
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-500</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-40600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>95500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>112300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>98600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-105800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>204800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>73000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-39500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-21100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-43300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-29500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>85100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-16300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>31900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-63600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>149000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-231900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-111400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>75600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>81000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>49500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>12800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>15400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-7000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
   <si>
     <t>YRD</t>
   </si>
@@ -1621,7 +1621,7 @@
         <v>102100</v>
       </c>
       <c r="H17" s="3">
-        <v>82800</v>
+        <v>83000</v>
       </c>
       <c r="I17" s="3">
         <v>83100</v>
@@ -1725,7 +1725,7 @@
         <v>88800</v>
       </c>
       <c r="H18" s="3">
-        <v>96900</v>
+        <v>96700</v>
       </c>
       <c r="I18" s="3">
         <v>96600</v>
@@ -1867,7 +1867,7 @@
         <v>7100</v>
       </c>
       <c r="H20" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="I20" s="3">
         <v>1900</v>
@@ -3115,7 +3115,7 @@
         <v>-7100</v>
       </c>
       <c r="H32" s="3">
-        <v>-700</v>
+        <v>-500</v>
       </c>
       <c r="I32" s="3">
         <v>-1900</v>
@@ -3808,7 +3808,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>10600</v>
+        <v>188000</v>
       </c>
       <c r="E42" s="3">
         <v>9000</v>
@@ -3912,7 +3912,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>740200</v>
+        <v>589700</v>
       </c>
       <c r="E43" s="3">
         <v>765200</v>
@@ -4120,7 +4120,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>65000</v>
+        <v>224500</v>
       </c>
       <c r="E45" s="3">
         <v>55800</v>
@@ -4132,7 +4132,7 @@
         <v>5100</v>
       </c>
       <c r="H45" s="3">
-        <v>28700</v>
+        <v>28000</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -4224,7 +4224,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1701200</v>
+        <v>1572000</v>
       </c>
       <c r="E46" s="3">
         <v>1707100</v>
@@ -4236,7 +4236,7 @@
         <v>1446100</v>
       </c>
       <c r="H46" s="3">
-        <v>1361200</v>
+        <v>1360600</v>
       </c>
       <c r="I46" s="3">
         <v>1208700</v>
@@ -4536,7 +4536,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -4548,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -4847,8 +4847,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>128600</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>8</v>
@@ -5236,7 +5236,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5900</v>
+        <v>23600</v>
       </c>
       <c r="E57" s="3">
         <v>6100</v>
@@ -5340,7 +5340,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17800</v>
+        <v>160100</v>
       </c>
       <c r="E59" s="3">
         <v>13800</v>
@@ -5548,7 +5548,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>245900</v>
+        <v>237400</v>
       </c>
       <c r="E60" s="3">
         <v>258200</v>
@@ -5652,7 +5652,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5600</v>
+        <v>3500</v>
       </c>
       <c r="E61" s="3">
         <v>2200</v>
@@ -5756,7 +5756,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>212900</v>
+        <v>223500</v>
       </c>
       <c r="E62" s="3">
         <v>187000</v>
@@ -8228,8 +8228,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>51100</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>8</v>
@@ -8682,8 +8682,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-4500</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>8</v>
@@ -9240,8 +9240,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-15700</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>8</v>
@@ -9449,7 +9449,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YRD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>YRD</t>
   </si>
@@ -656,466 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
+        <v>214200</v>
+      </c>
+      <c r="F8" s="3">
         <v>199000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>210900</v>
       </c>
-      <c r="F8" s="3">
-        <v>205900</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3">
         <v>190900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>179700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>179600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>182600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>143600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>153400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>116200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>208100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>141900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>170100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>159900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>156400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>166700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>142400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>105100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>149500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>388500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>316600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>345800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>302600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>431100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>317700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>418100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>540200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>270800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>224700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>175600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>148600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>155800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>127500</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
+        <v>31000</v>
+      </c>
+      <c r="F9" s="3">
         <v>27000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>29400</v>
       </c>
-      <c r="F9" s="3">
-        <v>33900</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3">
         <v>32300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>26000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>33600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>47800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>29100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>29800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>30900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>47200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>30100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>25800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>26000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>24800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>85700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>33400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>23000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>15000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>26800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>24000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>25400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>26300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>33000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>38100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>43000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>38000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>21800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>17700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>13800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>8500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>183300</v>
+      </c>
+      <c r="F10" s="3">
         <v>171900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>181500</v>
       </c>
-      <c r="F10" s="3">
-        <v>172000</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3">
         <v>158600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>153700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>146000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>134800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>114500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>123600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>85300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>160900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>111800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>144300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>134000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>131600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>81000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>109000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>82100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>134500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>361700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>292600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>320400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>276300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>398100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>279600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>375100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>502200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>249000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>207000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>161800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>140000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>147500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>120600</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1152,41 +1178,43 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F12" s="3">
         <v>22600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>21500</v>
       </c>
-      <c r="F12" s="3">
-        <v>7700</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>5600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>6700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>5300</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>4200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1256,8 +1284,14 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,8 +1394,14 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1389,36 +1429,36 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>94200</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1431,11 +1471,11 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1464,41 +1504,47 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
         <v>300</v>
       </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
+        <v>300</v>
+      </c>
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1568,8 +1614,14 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1603,216 +1655,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
+        <v>115200</v>
+      </c>
+      <c r="F17" s="3">
         <v>124100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>123700</v>
       </c>
-      <c r="F17" s="3">
-        <v>107300</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3">
         <v>102100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>83000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>83100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>90000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>63800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>64300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>69800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>138400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>96200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>112800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>119500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>119500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>248700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>126600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>141300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>147800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>286800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>281700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>319500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>267200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>295500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>341600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>406400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>455900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>191700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>168600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>120200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>91400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>98100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>95900</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
+        <v>99000</v>
+      </c>
+      <c r="F18" s="3">
         <v>74900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>87200</v>
       </c>
-      <c r="F18" s="3">
-        <v>98700</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3">
         <v>88800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>96700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>96600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>92600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>79800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>89100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>46400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>69700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>45700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>57300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>40400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>36800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-82000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>15800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-36200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>101700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>34900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>26300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>35400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>135600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-23900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>11700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>84200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>79100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>56100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>55400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>57100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>57700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1849,216 +1915,230 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
+        <v>64600</v>
+      </c>
+      <c r="F20" s="3">
         <v>32300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>33300</v>
       </c>
-      <c r="F20" s="3">
-        <v>33100</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>7100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J20" s="3">
-        <v>2000</v>
       </c>
       <c r="K20" s="3">
         <v>1900</v>
       </c>
       <c r="L20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N20" s="3">
         <v>1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-4100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-4800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-6100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-2400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-2700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-27000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>3300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>7400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>32700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>12300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>9300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>21400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>4700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>2000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>1600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>3900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>3700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>34700</v>
+      </c>
+      <c r="F21" s="3">
         <v>43000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>54300</v>
       </c>
-      <c r="F21" s="3">
-        <v>65900</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>82000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>96500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>94900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>90800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>78200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>90000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>46100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>72700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>45100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>54300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>35900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>34200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-89000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>13300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-39300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>7300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>76700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>38300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>33500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>73100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>164200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-14800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>33000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>94400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>81200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>58000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>59400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>61500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>59800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2086,11 +2166,11 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2161,216 +2241,234 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
+        <v>37700</v>
+      </c>
+      <c r="F23" s="3">
         <v>46900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>57000</v>
       </c>
-      <c r="F23" s="3">
-        <v>69000</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3">
         <v>85500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>100400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>98200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>92000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>80000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>90900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>47000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>70500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>45200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>54800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>36300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>32100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-88000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>13400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-38900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>3400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>74700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>38200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>33700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>68100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>147900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>33100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>88900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>81100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>57700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>59300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>60900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>59700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F24" s="3">
         <v>1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>6400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3">
+        <v>18300</v>
+      </c>
+      <c r="J24" s="3">
+        <v>19900</v>
+      </c>
+      <c r="K24" s="3">
+        <v>22200</v>
+      </c>
+      <c r="L24" s="3">
+        <v>19300</v>
+      </c>
+      <c r="M24" s="3">
+        <v>17900</v>
+      </c>
+      <c r="N24" s="3">
+        <v>22500</v>
+      </c>
+      <c r="O24" s="3">
+        <v>9700</v>
+      </c>
+      <c r="P24" s="3">
+        <v>9800</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>-700</v>
+      </c>
+      <c r="R24" s="3">
+        <v>10500</v>
+      </c>
+      <c r="S24" s="3">
+        <v>7900</v>
+      </c>
+      <c r="T24" s="3">
+        <v>6300</v>
+      </c>
+      <c r="U24" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="V24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="W24" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="X24" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>12500</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>11700</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>14500</v>
+      </c>
+      <c r="AH24" s="3">
         <v>12700</v>
       </c>
-      <c r="G24" s="3">
-        <v>18300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>19900</v>
-      </c>
-      <c r="I24" s="3">
-        <v>22200</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="AI24" s="3">
         <v>19300</v>
       </c>
-      <c r="K24" s="3">
-        <v>17900</v>
-      </c>
-      <c r="L24" s="3">
-        <v>22500</v>
-      </c>
-      <c r="M24" s="3">
-        <v>9700</v>
-      </c>
-      <c r="N24" s="3">
-        <v>9800</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-700</v>
-      </c>
-      <c r="P24" s="3">
-        <v>10500</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>7900</v>
-      </c>
-      <c r="R24" s="3">
-        <v>6300</v>
-      </c>
-      <c r="S24" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="T24" s="3">
-        <v>2300</v>
-      </c>
-      <c r="U24" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="V24" s="3">
-        <v>600</v>
-      </c>
-      <c r="W24" s="3">
-        <v>12500</v>
-      </c>
-      <c r="X24" s="3">
-        <v>3100</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>9700</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>11700</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>4700</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>5100</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>6000</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>12000</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>14500</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>12700</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>19300</v>
-      </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>9900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>-19200</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2473,216 +2571,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
+        <v>34100</v>
+      </c>
+      <c r="F26" s="3">
         <v>45400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>50700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3">
+        <v>67300</v>
+      </c>
+      <c r="J26" s="3">
+        <v>80600</v>
+      </c>
+      <c r="K26" s="3">
+        <v>76000</v>
+      </c>
+      <c r="L26" s="3">
+        <v>72700</v>
+      </c>
+      <c r="M26" s="3">
+        <v>62200</v>
+      </c>
+      <c r="N26" s="3">
+        <v>68400</v>
+      </c>
+      <c r="O26" s="3">
+        <v>37300</v>
+      </c>
+      <c r="P26" s="3">
+        <v>60700</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>46000</v>
+      </c>
+      <c r="R26" s="3">
+        <v>44300</v>
+      </c>
+      <c r="S26" s="3">
+        <v>28400</v>
+      </c>
+      <c r="T26" s="3">
+        <v>25800</v>
+      </c>
+      <c r="U26" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="V26" s="3">
+        <v>11100</v>
+      </c>
+      <c r="W26" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="X26" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>62200</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>35100</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>24100</v>
+      </c>
+      <c r="AB26" s="3">
         <v>56400</v>
       </c>
-      <c r="G26" s="3">
-        <v>67300</v>
-      </c>
-      <c r="H26" s="3">
-        <v>80600</v>
-      </c>
-      <c r="I26" s="3">
-        <v>76000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>72700</v>
-      </c>
-      <c r="K26" s="3">
-        <v>62200</v>
-      </c>
-      <c r="L26" s="3">
-        <v>68400</v>
-      </c>
-      <c r="M26" s="3">
-        <v>37300</v>
-      </c>
-      <c r="N26" s="3">
-        <v>60700</v>
-      </c>
-      <c r="O26" s="3">
-        <v>46000</v>
-      </c>
-      <c r="P26" s="3">
-        <v>44300</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>28400</v>
-      </c>
-      <c r="R26" s="3">
-        <v>25800</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-80400</v>
-      </c>
-      <c r="T26" s="3">
-        <v>11100</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-32300</v>
-      </c>
-      <c r="V26" s="3">
-        <v>2800</v>
-      </c>
-      <c r="W26" s="3">
-        <v>62200</v>
-      </c>
-      <c r="X26" s="3">
-        <v>35100</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>24100</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>56400</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>143200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>27100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>76900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>66600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>45000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>39900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>51000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>55200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
+        <v>34100</v>
+      </c>
+      <c r="F27" s="3">
         <v>45400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>50700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3">
+        <v>67300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>80600</v>
+      </c>
+      <c r="K27" s="3">
+        <v>76000</v>
+      </c>
+      <c r="L27" s="3">
+        <v>72700</v>
+      </c>
+      <c r="M27" s="3">
+        <v>62200</v>
+      </c>
+      <c r="N27" s="3">
+        <v>68400</v>
+      </c>
+      <c r="O27" s="3">
+        <v>37300</v>
+      </c>
+      <c r="P27" s="3">
+        <v>60700</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>46000</v>
+      </c>
+      <c r="R27" s="3">
+        <v>44300</v>
+      </c>
+      <c r="S27" s="3">
+        <v>28400</v>
+      </c>
+      <c r="T27" s="3">
+        <v>25800</v>
+      </c>
+      <c r="U27" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="V27" s="3">
+        <v>11100</v>
+      </c>
+      <c r="W27" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="X27" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>62200</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>35100</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>24100</v>
+      </c>
+      <c r="AB27" s="3">
         <v>56400</v>
       </c>
-      <c r="G27" s="3">
-        <v>67300</v>
-      </c>
-      <c r="H27" s="3">
-        <v>80600</v>
-      </c>
-      <c r="I27" s="3">
-        <v>76000</v>
-      </c>
-      <c r="J27" s="3">
-        <v>72700</v>
-      </c>
-      <c r="K27" s="3">
-        <v>62200</v>
-      </c>
-      <c r="L27" s="3">
-        <v>68400</v>
-      </c>
-      <c r="M27" s="3">
-        <v>37300</v>
-      </c>
-      <c r="N27" s="3">
-        <v>60700</v>
-      </c>
-      <c r="O27" s="3">
-        <v>46000</v>
-      </c>
-      <c r="P27" s="3">
-        <v>44300</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>28400</v>
-      </c>
-      <c r="R27" s="3">
-        <v>25800</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-80400</v>
-      </c>
-      <c r="T27" s="3">
-        <v>11100</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-32300</v>
-      </c>
-      <c r="V27" s="3">
-        <v>2800</v>
-      </c>
-      <c r="W27" s="3">
-        <v>62200</v>
-      </c>
-      <c r="X27" s="3">
-        <v>35100</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>24100</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>56400</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>143200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>27100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>76900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>66600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>45000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>39900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>51000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>55200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2785,8 +2901,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2889,8 +3011,14 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,8 +3121,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3097,216 +3231,234 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-32300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-33300</v>
       </c>
-      <c r="F32" s="3">
-        <v>-33100</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>-7100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-2000</v>
       </c>
       <c r="K32" s="3">
         <v>-1900</v>
       </c>
       <c r="L32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>2500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>4100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>4800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>6100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>2400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>2700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>27000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-32700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-9300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-21400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
+        <v>34100</v>
+      </c>
+      <c r="F33" s="3">
         <v>45400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>50700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3">
+        <v>67300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>80600</v>
+      </c>
+      <c r="K33" s="3">
+        <v>76000</v>
+      </c>
+      <c r="L33" s="3">
+        <v>72700</v>
+      </c>
+      <c r="M33" s="3">
+        <v>62200</v>
+      </c>
+      <c r="N33" s="3">
+        <v>68400</v>
+      </c>
+      <c r="O33" s="3">
+        <v>37300</v>
+      </c>
+      <c r="P33" s="3">
+        <v>60700</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>46000</v>
+      </c>
+      <c r="R33" s="3">
+        <v>44300</v>
+      </c>
+      <c r="S33" s="3">
+        <v>28400</v>
+      </c>
+      <c r="T33" s="3">
+        <v>25800</v>
+      </c>
+      <c r="U33" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="V33" s="3">
+        <v>11100</v>
+      </c>
+      <c r="W33" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="X33" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>62200</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>35100</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>24100</v>
+      </c>
+      <c r="AB33" s="3">
         <v>56400</v>
       </c>
-      <c r="G33" s="3">
-        <v>67300</v>
-      </c>
-      <c r="H33" s="3">
-        <v>80600</v>
-      </c>
-      <c r="I33" s="3">
-        <v>76000</v>
-      </c>
-      <c r="J33" s="3">
-        <v>72700</v>
-      </c>
-      <c r="K33" s="3">
-        <v>62200</v>
-      </c>
-      <c r="L33" s="3">
-        <v>68400</v>
-      </c>
-      <c r="M33" s="3">
-        <v>37300</v>
-      </c>
-      <c r="N33" s="3">
-        <v>60700</v>
-      </c>
-      <c r="O33" s="3">
-        <v>46000</v>
-      </c>
-      <c r="P33" s="3">
-        <v>44300</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>28400</v>
-      </c>
-      <c r="R33" s="3">
-        <v>25800</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-80400</v>
-      </c>
-      <c r="T33" s="3">
-        <v>11100</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-32300</v>
-      </c>
-      <c r="V33" s="3">
-        <v>2800</v>
-      </c>
-      <c r="W33" s="3">
-        <v>62200</v>
-      </c>
-      <c r="X33" s="3">
-        <v>35100</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>24100</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>56400</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>143200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>27100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>76900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>66600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>45000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>39900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>51000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>55200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3409,221 +3561,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
+        <v>34100</v>
+      </c>
+      <c r="F35" s="3">
         <v>45400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>50700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3">
+        <v>67300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>80600</v>
+      </c>
+      <c r="K35" s="3">
+        <v>76000</v>
+      </c>
+      <c r="L35" s="3">
+        <v>72700</v>
+      </c>
+      <c r="M35" s="3">
+        <v>62200</v>
+      </c>
+      <c r="N35" s="3">
+        <v>68400</v>
+      </c>
+      <c r="O35" s="3">
+        <v>37300</v>
+      </c>
+      <c r="P35" s="3">
+        <v>60700</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>46000</v>
+      </c>
+      <c r="R35" s="3">
+        <v>44300</v>
+      </c>
+      <c r="S35" s="3">
+        <v>28400</v>
+      </c>
+      <c r="T35" s="3">
+        <v>25800</v>
+      </c>
+      <c r="U35" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="V35" s="3">
+        <v>11100</v>
+      </c>
+      <c r="W35" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="X35" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>62200</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>35100</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>24100</v>
+      </c>
+      <c r="AB35" s="3">
         <v>56400</v>
       </c>
-      <c r="G35" s="3">
-        <v>67300</v>
-      </c>
-      <c r="H35" s="3">
-        <v>80600</v>
-      </c>
-      <c r="I35" s="3">
-        <v>76000</v>
-      </c>
-      <c r="J35" s="3">
-        <v>72700</v>
-      </c>
-      <c r="K35" s="3">
-        <v>62200</v>
-      </c>
-      <c r="L35" s="3">
-        <v>68400</v>
-      </c>
-      <c r="M35" s="3">
-        <v>37300</v>
-      </c>
-      <c r="N35" s="3">
-        <v>60700</v>
-      </c>
-      <c r="O35" s="3">
-        <v>46000</v>
-      </c>
-      <c r="P35" s="3">
-        <v>44300</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>28400</v>
-      </c>
-      <c r="R35" s="3">
-        <v>25800</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-80400</v>
-      </c>
-      <c r="T35" s="3">
-        <v>11100</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-32300</v>
-      </c>
-      <c r="V35" s="3">
-        <v>2800</v>
-      </c>
-      <c r="W35" s="3">
-        <v>62200</v>
-      </c>
-      <c r="X35" s="3">
-        <v>35100</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>24100</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>56400</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>143200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>27100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>76900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>66600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>45000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>39900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>51000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>55200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3660,8 +3830,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3698,139 +3870,147 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
+        <v>557200</v>
+      </c>
+      <c r="F41" s="3">
         <v>526300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>528300</v>
       </c>
-      <c r="F41" s="3">
-        <v>756400</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3">
         <v>817700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>816700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>745300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>801000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>739100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>602300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>499200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>601600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>398200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>321500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>311700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>335800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>354700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>394800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>408600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>466600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>492400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>405400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>422200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>384900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>378600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>117200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>79400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>239200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>275600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>208300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>132300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>125700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>140800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>160900</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>188000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>9000</v>
       </c>
-      <c r="F42" s="3">
-        <v>11500</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>10800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>57000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>10200</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3906,112 +4086,124 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
+        <v>733000</v>
+      </c>
+      <c r="F43" s="3">
         <v>589700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>765200</v>
       </c>
-      <c r="F43" s="3">
-        <v>499600</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3">
         <v>423800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>418700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>397000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>406600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>401600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>209700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>193300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>170400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>164600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>141900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>183800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>150700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>144600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>234500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>221000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>236200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>152800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>268800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>283700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>52100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>203600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>18700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>17700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>20100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>20600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>29800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>3300</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK43" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ43" s="3" t="s">
+      <c r="AL43" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4039,11 +4231,11 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4114,145 +4306,157 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
+        <v>85500</v>
+      </c>
+      <c r="F45" s="3">
         <v>224500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>55800</v>
       </c>
-      <c r="F45" s="3">
-        <v>35900</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>5100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>28000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>45300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>49900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>36800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>48900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>49400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>30400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>30600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>40000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>137400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>157900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>126800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>205300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>197200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>178300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>186600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>370700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>171500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>171900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>170900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>158600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>168700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>91700</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK45" s="3">
         <v>67900</v>
       </c>
-      <c r="AJ45" s="3" t="s">
+      <c r="AL45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1735700</v>
+      </c>
+      <c r="F46" s="3">
         <v>1572000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1707100</v>
       </c>
-      <c r="F46" s="3">
-        <v>1560000</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3">
         <v>1446100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1360600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1208700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1250700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1186400</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4322,240 +4526,258 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
+        <v>56900</v>
+      </c>
+      <c r="F47" s="3">
         <v>50600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>47600</v>
       </c>
-      <c r="F47" s="3">
-        <v>46400</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>54000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>63300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>47000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>14900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>37000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>306000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>323100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>256000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>425000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>486500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>446600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>398400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>341000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>305200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>302800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>391500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>510400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>578100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>655400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>909100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>968300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>688300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>707400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>617000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>261900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>255800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>314900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>297700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>236800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>16200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>16200</v>
+      </c>
+      <c r="G48" s="3">
         <v>13500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3">
         <v>13400</v>
       </c>
-      <c r="G48" s="3">
-        <v>13400</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>14500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>13800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>13700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>15300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>15700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>16800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>19500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>25500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>25700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>30900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>33100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>36300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>45200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>56900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>70100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>81600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>92000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>98000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>96100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>38600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>14000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>13500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>11900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>12200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>12100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>8900</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK48" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ48" s="3" t="s">
+      <c r="AL48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3">
+        <v>20400</v>
+      </c>
+      <c r="F49" s="3">
         <v>700</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>700</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
@@ -4634,8 +4856,14 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4738,8 +4966,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4842,20 +5076,26 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3">
         <v>128600</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4871,83 +5111,89 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3">
         <v>24400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>20900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>20500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>12300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>13500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>13800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>29800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>36500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>30900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>19500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>12400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>17900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>36100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>41400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>38800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>88800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>50000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>152900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>290800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>386900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>361500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>337900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>205100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>240600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>141700</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5050,112 +5296,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1829300</v>
+      </c>
+      <c r="F54" s="3">
         <v>1778700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1776000</v>
       </c>
-      <c r="F54" s="3">
-        <v>1626000</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3">
         <v>1521600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1449300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1281600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1292100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1252000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1203400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1103400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1105200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1075900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1043400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1023500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>987300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>962600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1165300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1187000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1325500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1485000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1599600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1701200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1689500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2069800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1059600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1142900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1349900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1115800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1036300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>888900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>782000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>695600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>586200</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5192,8 +5450,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5230,145 +5490,153 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F57" s="3">
         <v>23600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>6100</v>
       </c>
-      <c r="F57" s="3">
-        <v>6000</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
         <v>5700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>9200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>5700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>6700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>9600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>8400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>8200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>44600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>4800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>5100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>5100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>5000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>3400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>2200</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK57" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ57" s="3" t="s">
+      <c r="AL57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>2100</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>2700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>46700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>36100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5438,145 +5706,157 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F59" s="3">
         <v>160100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>13800</v>
       </c>
-      <c r="F59" s="3">
-        <v>300</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>153700</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>222500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>215500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>242200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>241900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>251900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>264100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>291000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>332300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>337200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>330000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>338400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>420000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>456400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>433100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>431000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1611500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>224200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>361500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>189000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>220600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>277900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>152400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>55300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>205500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>51700</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
+        <v>216800</v>
+      </c>
+      <c r="F60" s="3">
         <v>237400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>258200</v>
       </c>
-      <c r="F60" s="3">
-        <v>244000</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3">
         <v>226800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>203600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>212300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>252700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>234400</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5646,65 +5926,71 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F61" s="3">
         <v>3500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2200</v>
       </c>
-      <c r="F61" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>2600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>57800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>61500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>108300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>106100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>120100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>143000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>143400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>137700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>113600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>71900</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5750,112 +6036,124 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3">
+        <v>255500</v>
+      </c>
+      <c r="F62" s="3">
         <v>223500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>187000</v>
       </c>
-      <c r="F62" s="3">
-        <v>132800</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
         <v>78700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>79900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>13700</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>11200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>10900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>11100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>15600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>20400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>16900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>10800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>5600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>20900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>22600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>31600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>33700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>41200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>51400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>63800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>70700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>81500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>92100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>90000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>8900</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5958,8 +6256,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6062,8 +6366,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6166,112 +6476,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
+        <v>485100</v>
+      </c>
+      <c r="F66" s="3">
         <v>471300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>452400</v>
       </c>
-      <c r="F66" s="3">
-        <v>392400</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3">
         <v>330400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>309000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>249700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>328700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>313500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>353200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>336900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>378600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>405700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>423200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>431800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>424600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>420000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>561000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>594000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>670600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>793700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1149400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1282900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1302400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2122600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>366300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>501700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>726100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>675100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>665900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>480400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>420000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>384400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>333000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6308,8 +6630,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6412,8 +6736,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6516,8 +6846,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6620,8 +6956,14 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6724,112 +7066,124 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
+        <v>645200</v>
+      </c>
+      <c r="F72" s="3">
         <v>607600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>602400</v>
       </c>
-      <c r="F72" s="3">
-        <v>533900</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
         <v>480700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>421000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>330900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>256600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>194300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>128100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>58600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>26200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-34500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-79800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-124900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-153100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-180600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-97000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-108100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-79200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-82100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-144200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-181100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-200200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>310400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>506800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>475500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>459100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>272300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>207200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>264700</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK72" s="3">
         <v>171200</v>
       </c>
-      <c r="AJ72" s="3" t="s">
+      <c r="AL72" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6932,8 +7286,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7036,8 +7396,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7140,112 +7506,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1344100</v>
+      </c>
+      <c r="F76" s="3">
         <v>1307300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1323700</v>
       </c>
-      <c r="F76" s="3">
-        <v>1233500</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3">
         <v>1191200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1140300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1031900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>963400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>938500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>850200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>766500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>726600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>670300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>620200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>591700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>562700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>542500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>604300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>593000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>654900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>691400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>450200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>418300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>387000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-52800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>693400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>641200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>623800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>440800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>370400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>408500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>361900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>311200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>253200</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7348,221 +7726,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
+        <v>34100</v>
+      </c>
+      <c r="F81" s="3">
         <v>45400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>50700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3">
+        <v>67300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>80600</v>
+      </c>
+      <c r="K81" s="3">
+        <v>76000</v>
+      </c>
+      <c r="L81" s="3">
+        <v>72700</v>
+      </c>
+      <c r="M81" s="3">
+        <v>62200</v>
+      </c>
+      <c r="N81" s="3">
+        <v>68400</v>
+      </c>
+      <c r="O81" s="3">
+        <v>37300</v>
+      </c>
+      <c r="P81" s="3">
+        <v>60700</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>46000</v>
+      </c>
+      <c r="R81" s="3">
+        <v>44300</v>
+      </c>
+      <c r="S81" s="3">
+        <v>28400</v>
+      </c>
+      <c r="T81" s="3">
+        <v>25800</v>
+      </c>
+      <c r="U81" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="V81" s="3">
+        <v>11100</v>
+      </c>
+      <c r="W81" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="X81" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Y81" s="3">
+        <v>62200</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>35100</v>
+      </c>
+      <c r="AA81" s="3">
+        <v>24100</v>
+      </c>
+      <c r="AB81" s="3">
         <v>56400</v>
       </c>
-      <c r="G81" s="3">
-        <v>67300</v>
-      </c>
-      <c r="H81" s="3">
-        <v>80600</v>
-      </c>
-      <c r="I81" s="3">
-        <v>76000</v>
-      </c>
-      <c r="J81" s="3">
-        <v>72700</v>
-      </c>
-      <c r="K81" s="3">
-        <v>62200</v>
-      </c>
-      <c r="L81" s="3">
-        <v>68400</v>
-      </c>
-      <c r="M81" s="3">
-        <v>37300</v>
-      </c>
-      <c r="N81" s="3">
-        <v>60700</v>
-      </c>
-      <c r="O81" s="3">
-        <v>46000</v>
-      </c>
-      <c r="P81" s="3">
-        <v>44300</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>28400</v>
-      </c>
-      <c r="R81" s="3">
-        <v>25800</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-80400</v>
-      </c>
-      <c r="T81" s="3">
-        <v>11100</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-32300</v>
-      </c>
-      <c r="V81" s="3">
-        <v>2800</v>
-      </c>
-      <c r="W81" s="3">
-        <v>62200</v>
-      </c>
-      <c r="X81" s="3">
-        <v>35100</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>24100</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>56400</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>143200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>27100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>76900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>66600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>45000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>39900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>51000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>55200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7599,41 +7995,43 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="3">
-        <v>200</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3">
+        <v>300</v>
+      </c>
+      <c r="J83" s="3">
         <v>4200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -7703,8 +8101,14 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7807,8 +8211,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7911,8 +8321,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8015,8 +8431,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8119,8 +8541,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8223,112 +8651,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="3">
-        <v>50800</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="E89" s="3">
+        <v>66000</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>87500</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>99000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>56800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>66500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>47400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>142900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>26300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>44700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-30300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-20200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-31500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>4200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-12100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>81400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>13600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>181100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-51800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-100600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>149000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-20100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-191800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-48500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>189300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>51400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>78700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>82100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>121600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>65500</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8365,8 +8805,10 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8394,11 +8836,11 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8469,8 +8911,14 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8573,8 +9021,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8677,112 +9131,124 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-73900</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="E94" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-94700</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3">
         <v>-2800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>112700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>39900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-115400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>83500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>53100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-29600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-40700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-140900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-17600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-22900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-76600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>314600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-199000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>91300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-34500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>127200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>322400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>65700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-37700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>50800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-14200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-62200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-117500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-98800</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8819,8 +9285,10 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8848,11 +9316,11 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8923,8 +9391,14 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9027,8 +9501,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9131,8 +9611,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9235,154 +9721,166 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-17300</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="E100" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>-2000</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-57200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-7700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-38200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-21900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-6400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>6900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>20500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>39700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>129200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>11400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>5600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-9600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-242800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>1100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>75400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-15300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>33900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-86300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-14100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-6500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="E101" s="3">
+        <v>200</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
@@ -9390,61 +9888,67 @@
         <v>0</v>
       </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-500</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>2200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>1100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>1300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9452,99 +9956,105 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>35100</v>
       </c>
       <c r="F102" s="3">
-        <v>-40600</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-9100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>95500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>112300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>98600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-105800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>204800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>73000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>19300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-39500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-21100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-43300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-29500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-4500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>85100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>31900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-63600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>149000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-231900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-111400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>75600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>81000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>49500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>12800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>15400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-7000</v>
       </c>
     </row>
